--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Aircraft_Cumulative_Statistics_2021.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Aircraft_Cumulative_Statistics_2021.xlsx
@@ -13,78 +13,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Breeze</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-500</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A220-100</t>
+  </si>
+  <si>
+    <t>A220-300</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A320NEO</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B737-9</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>A330-900</t>
+  </si>
+  <si>
+    <t>A350-900</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B787-10</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -166,10 +205,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -189,40 +228,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -230,40 +269,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>33756279607</v>
+        <v>3562562849</v>
       </c>
       <c r="C2" s="0">
-        <v>45742477174</v>
+        <v>4655109479</v>
       </c>
       <c r="D2" s="0">
-        <v>652439</v>
+        <v>48842</v>
       </c>
       <c r="E2" s="0">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>200673</v>
+        <v>280413</v>
       </c>
       <c r="G2" s="0">
-        <v>2.8599999999999999</v>
+        <v>2.9399999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>9.6400000000000006</v>
+        <v>4.2199999999999998</v>
       </c>
       <c r="I2" s="0">
-        <v>73.799999999999997</v>
+        <v>76.530000000000001</v>
       </c>
       <c r="J2" s="0">
-        <v>1351</v>
+        <v>332</v>
       </c>
       <c r="K2" s="0">
-        <v>4197</v>
+        <v>1588.6700000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>24.949999999999999</v>
+        <v>31.780000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.13700000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -271,40 +310,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>12174556934</v>
+        <v>3589076503</v>
       </c>
       <c r="C3" s="0">
-        <v>17204307366</v>
+        <v>5144234346</v>
       </c>
       <c r="D3" s="0">
-        <v>457561</v>
+        <v>56117</v>
       </c>
       <c r="E3" s="0">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>113186</v>
+        <v>288283</v>
       </c>
       <c r="G3" s="0">
-        <v>3.0099999999999998</v>
+        <v>3.1400000000000001</v>
       </c>
       <c r="H3" s="0">
-        <v>6.8899999999999997</v>
+        <v>4.3300000000000001</v>
       </c>
       <c r="I3" s="0">
-        <v>70.760000000000005</v>
+        <v>69.769999999999996</v>
       </c>
       <c r="J3" s="0">
-        <v>870</v>
+        <v>357</v>
       </c>
       <c r="K3" s="0">
-        <v>4008</v>
+        <v>2296.3499999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>22.960000000000001</v>
+        <v>45.93</v>
       </c>
       <c r="M3" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.17699999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -312,40 +351,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>136498444357</v>
+        <v>1598831898</v>
       </c>
       <c r="C4" s="0">
-        <v>182134049330</v>
+        <v>2014598782</v>
       </c>
       <c r="D4" s="0">
-        <v>595384</v>
+        <v>89737</v>
       </c>
       <c r="E4" s="0">
-        <v>172</v>
+        <v>70</v>
       </c>
       <c r="F4" s="0">
-        <v>864939</v>
+        <v>48856</v>
       </c>
       <c r="G4" s="0">
-        <v>2.8300000000000001</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="H4" s="0">
-        <v>8.3699999999999992</v>
+        <v>4.3200000000000003</v>
       </c>
       <c r="I4" s="0">
-        <v>74.939999999999998</v>
+        <v>79.359999999999999</v>
       </c>
       <c r="J4" s="0">
-        <v>1151</v>
+        <v>591</v>
       </c>
       <c r="K4" s="0">
-        <v>6387</v>
+        <v>1299.4100000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>35.520000000000003</v>
+        <v>18.620000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="5">
@@ -353,40 +392,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>115535801</v>
+        <v>31383781010</v>
       </c>
       <c r="C5" s="0">
-        <v>206185838</v>
+        <v>41540640374</v>
       </c>
       <c r="D5" s="0">
-        <v>65535</v>
+        <v>142800</v>
       </c>
       <c r="E5" s="0">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="F5" s="0">
-        <v>3513</v>
+        <v>906234</v>
       </c>
       <c r="G5" s="0">
-        <v>65535</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>65535</v>
+        <v>6.0700000000000003</v>
       </c>
       <c r="I5" s="0">
-        <v>56.030000000000001</v>
+        <v>75.549999999999997</v>
       </c>
       <c r="J5" s="0">
-        <v>546</v>
+        <v>614</v>
       </c>
       <c r="K5" s="0">
-        <v>0</v>
+        <v>1379.3800000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>0</v>
+        <v>18.48</v>
       </c>
       <c r="M5" s="0">
-        <v>0</v>
+        <v>0.058999999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -394,40 +433,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>121248228670</v>
+        <v>1004554080</v>
       </c>
       <c r="C6" s="0">
-        <v>175431026685</v>
+        <v>1241697900</v>
       </c>
       <c r="D6" s="0">
-        <v>620555</v>
+        <v>69137</v>
       </c>
       <c r="E6" s="0">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F6" s="0">
-        <v>836374</v>
+        <v>59901</v>
       </c>
       <c r="G6" s="0">
-        <v>2.96</v>
+        <v>3.3399999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>8.3000000000000007</v>
+        <v>5.3499999999999996</v>
       </c>
       <c r="I6" s="0">
-        <v>69.109999999999999</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="J6" s="0">
-        <v>1111</v>
+        <v>415</v>
       </c>
       <c r="K6" s="0">
-        <v>5432</v>
+        <v>2045.0999999999999</v>
       </c>
       <c r="L6" s="0">
-        <v>29.460000000000001</v>
+        <v>40.899999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +474,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>20364786986</v>
+        <v>6714160960</v>
       </c>
       <c r="C7" s="0">
-        <v>26850758906</v>
+        <v>8944331084</v>
       </c>
       <c r="D7" s="0">
-        <v>693281</v>
+        <v>117813</v>
       </c>
       <c r="E7" s="0">
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="F7" s="0">
-        <v>143467</v>
+        <v>274585</v>
       </c>
       <c r="G7" s="0">
-        <v>3.7000000000000002</v>
+        <v>3.6200000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>9.8399999999999999</v>
+        <v>6.2300000000000004</v>
       </c>
       <c r="I7" s="0">
-        <v>75.840000000000003</v>
+        <v>75.069999999999993</v>
       </c>
       <c r="J7" s="0">
-        <v>967</v>
+        <v>495</v>
       </c>
       <c r="K7" s="0">
-        <v>4474</v>
+        <v>1944.04</v>
       </c>
       <c r="L7" s="0">
-        <v>23.140000000000001</v>
+        <v>29.539999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +515,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>10005093987</v>
+        <v>3549912290</v>
       </c>
       <c r="C8" s="0">
-        <v>14458629851</v>
+        <v>4709209138</v>
       </c>
       <c r="D8" s="0">
-        <v>648951</v>
+        <v>215032</v>
       </c>
       <c r="E8" s="0">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="F8" s="0">
-        <v>61368</v>
+        <v>73074</v>
       </c>
       <c r="G8" s="0">
-        <v>2.75</v>
+        <v>3.3399999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>7</v>
+        <v>6.5300000000000002</v>
       </c>
       <c r="I8" s="0">
-        <v>69.200000000000003</v>
+        <v>75.379999999999995</v>
       </c>
       <c r="J8" s="0">
-        <v>1046</v>
+        <v>642</v>
       </c>
       <c r="K8" s="0">
-        <v>6921</v>
+        <v>4575.6700000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>32.32</v>
+        <v>45.619999999999997</v>
       </c>
       <c r="M8" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.13900000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -517,40 +556,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>41191549602</v>
+        <v>12010167044</v>
       </c>
       <c r="C9" s="0">
-        <v>54165076177</v>
+        <v>15999576473</v>
       </c>
       <c r="D9" s="0">
-        <v>543608</v>
+        <v>161743</v>
       </c>
       <c r="E9" s="0">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="F9" s="0">
-        <v>265619</v>
+        <v>446531</v>
       </c>
       <c r="G9" s="0">
-        <v>2.6699999999999999</v>
+        <v>4.5099999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>8.6099999999999994</v>
+        <v>7.4100000000000001</v>
       </c>
       <c r="I9" s="0">
-        <v>76.049999999999997</v>
+        <v>75.069999999999993</v>
       </c>
       <c r="J9" s="0">
-        <v>1278</v>
+        <v>474</v>
       </c>
       <c r="K9" s="0">
-        <v>4710</v>
+        <v>1513.45</v>
       </c>
       <c r="L9" s="0">
-        <v>29.870000000000001</v>
+        <v>20.030000000000001</v>
       </c>
       <c r="M9" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="10">
@@ -558,40 +597,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>103581393091</v>
+        <v>3319238941</v>
       </c>
       <c r="C10" s="0">
-        <v>132029420525</v>
+        <v>4353176458</v>
       </c>
       <c r="D10" s="0">
-        <v>495736</v>
+        <v>296740</v>
       </c>
       <c r="E10" s="0">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="F10" s="0">
-        <v>1066596</v>
+        <v>40951</v>
       </c>
       <c r="G10" s="0">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="H10" s="0">
-        <v>8.4499999999999993</v>
+        <v>7.29</v>
       </c>
       <c r="I10" s="0">
-        <v>78.450000000000003</v>
+        <v>76.25</v>
       </c>
       <c r="J10" s="0">
-        <v>791</v>
+        <v>975</v>
       </c>
       <c r="K10" s="0">
-        <v>4005</v>
+        <v>4416.4200000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>25.649999999999999</v>
+        <v>40.530000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +638,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>32126066583</v>
+        <v>1187889565</v>
       </c>
       <c r="C11" s="0">
-        <v>40753049115</v>
+        <v>1558931519</v>
       </c>
       <c r="D11" s="0">
-        <v>683317</v>
+        <v>385874</v>
       </c>
       <c r="E11" s="0">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="F11" s="0">
-        <v>211779</v>
+        <v>11756</v>
       </c>
       <c r="G11" s="0">
-        <v>3.5499999999999998</v>
+        <v>2.9100000000000001</v>
       </c>
       <c r="H11" s="0">
-        <v>9.6300000000000008</v>
+        <v>7.9000000000000004</v>
       </c>
       <c r="I11" s="0">
-        <v>78.829999999999998</v>
+        <v>76.200000000000003</v>
       </c>
       <c r="J11" s="0">
-        <v>1032</v>
+        <v>1000</v>
       </c>
       <c r="K11" s="0">
-        <v>3981</v>
+        <v>4434.75</v>
       </c>
       <c r="L11" s="0">
-        <v>21.34</v>
+        <v>33.460000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +679,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>3874332842</v>
+        <v>29748111048</v>
       </c>
       <c r="C12" s="0">
-        <v>5565309602</v>
+        <v>38967063060</v>
       </c>
       <c r="D12" s="0">
-        <v>344388</v>
+        <v>329922</v>
       </c>
       <c r="E12" s="0">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="F12" s="0">
-        <v>25548</v>
+        <v>344929</v>
       </c>
       <c r="G12" s="0">
-        <v>1.5800000000000001</v>
+        <v>2.9199999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>4.7300000000000004</v>
+        <v>6.8799999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>69.620000000000005</v>
+        <v>76.340000000000003</v>
       </c>
       <c r="J12" s="0">
-        <v>1191</v>
+        <v>851</v>
       </c>
       <c r="K12" s="0">
-        <v>4441</v>
+        <v>4431.6000000000004</v>
       </c>
       <c r="L12" s="0">
-        <v>24.260000000000002</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="M12" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +720,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>110698392154</v>
+        <v>66054316806</v>
       </c>
       <c r="C13" s="0">
-        <v>155722405468</v>
+        <v>87801329700</v>
       </c>
       <c r="D13" s="0">
-        <v>537771</v>
+        <v>478195</v>
       </c>
       <c r="E13" s="0">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F13" s="0">
-        <v>557940</v>
+        <v>540471</v>
       </c>
       <c r="G13" s="0">
-        <v>1.9299999999999999</v>
+        <v>2.9399999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>6.7400000000000002</v>
+        <v>7.7000000000000002</v>
       </c>
       <c r="I13" s="0">
-        <v>71.090000000000003</v>
+        <v>75.230000000000004</v>
       </c>
       <c r="J13" s="0">
-        <v>1453</v>
+        <v>988</v>
       </c>
       <c r="K13" s="0">
-        <v>6425</v>
+        <v>4896.0200000000004</v>
       </c>
       <c r="L13" s="0">
-        <v>34.359999999999999</v>
+        <v>29.800000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +761,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1196165489</v>
+        <v>21123211863</v>
       </c>
       <c r="C14" s="0">
-        <v>1534650900</v>
+        <v>27477820744</v>
       </c>
       <c r="D14" s="0">
-        <v>66320</v>
+        <v>670845</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="F14" s="0">
-        <v>75877</v>
+        <v>147702</v>
       </c>
       <c r="G14" s="0">
-        <v>3.2799999999999998</v>
+        <v>3.6099999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>5.1600000000000001</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="I14" s="0">
-        <v>77.939999999999998</v>
+        <v>76.870000000000005</v>
       </c>
       <c r="J14" s="0">
-        <v>405</v>
+        <v>1009</v>
       </c>
       <c r="K14" s="0">
-        <v>1483</v>
+        <v>4174.4300000000003</v>
       </c>
       <c r="L14" s="0">
-        <v>29.670000000000002</v>
+        <v>22.629999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>0.12</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +802,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5294154068</v>
+        <v>87086883349</v>
       </c>
       <c r="C15" s="0">
-        <v>7451023804</v>
+        <v>110394550101</v>
       </c>
       <c r="D15" s="0">
-        <v>109978</v>
+        <v>669301</v>
       </c>
       <c r="E15" s="0">
-        <v>67</v>
+        <v>191</v>
       </c>
       <c r="F15" s="0">
-        <v>273236</v>
+        <v>512547</v>
       </c>
       <c r="G15" s="0">
-        <v>4.0300000000000002</v>
+        <v>3.1099999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>5.7199999999999998</v>
+        <v>9.1699999999999999</v>
       </c>
       <c r="I15" s="0">
-        <v>71.049999999999997</v>
+        <v>78.890000000000001</v>
       </c>
       <c r="J15" s="0">
-        <v>392</v>
+        <v>1148</v>
       </c>
       <c r="K15" s="0">
-        <v>1447</v>
+        <v>5336.0200000000004</v>
       </c>
       <c r="L15" s="0">
-        <v>21.09</v>
+        <v>28.309999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +843,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>7341723801</v>
+        <v>18350821703</v>
       </c>
       <c r="C16" s="0">
-        <v>9406748776</v>
+        <v>24523726632</v>
       </c>
       <c r="D16" s="0">
-        <v>54907</v>
+        <v>879617</v>
       </c>
       <c r="E16" s="0">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="F16" s="0">
-        <v>264911</v>
+        <v>68317</v>
       </c>
       <c r="G16" s="0">
-        <v>1.55</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H16" s="0">
-        <v>2.6899999999999999</v>
+        <v>10.59</v>
       </c>
       <c r="I16" s="0">
-        <v>78.049999999999997</v>
+        <v>74.829999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>510</v>
+        <v>1857</v>
       </c>
       <c r="K16" s="0">
-        <v>1598</v>
+        <v>5318.9099999999999</v>
       </c>
       <c r="L16" s="0">
-        <v>23.530000000000001</v>
+        <v>27.489999999999998</v>
       </c>
       <c r="M16" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +884,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1004554080</v>
+        <v>3741015240</v>
       </c>
       <c r="C17" s="0">
-        <v>1241697900</v>
+        <v>5152156687</v>
       </c>
       <c r="D17" s="0">
-        <v>69137</v>
+        <v>200239</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F17" s="0">
-        <v>59901</v>
+        <v>127759</v>
       </c>
       <c r="G17" s="0">
-        <v>3.3399999999999999</v>
+        <v>4.9699999999999998</v>
       </c>
       <c r="H17" s="0">
-        <v>5.3499999999999996</v>
+        <v>6.2400000000000002</v>
       </c>
       <c r="I17" s="0">
-        <v>80.900000000000006</v>
+        <v>72.609999999999999</v>
       </c>
       <c r="J17" s="0">
-        <v>415</v>
+        <v>360</v>
       </c>
       <c r="K17" s="0">
-        <v>2045</v>
+        <v>4668.29</v>
       </c>
       <c r="L17" s="0">
-        <v>40.899999999999999</v>
+        <v>41.229999999999997</v>
       </c>
       <c r="M17" s="0">
-        <v>0.16</v>
+        <v>0.14499999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +925,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1880416375</v>
+        <v>60066323335</v>
       </c>
       <c r="C18" s="0">
-        <v>2573752996</v>
+        <v>76096708575</v>
       </c>
       <c r="D18" s="0">
-        <v>134470</v>
+        <v>403332</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="F18" s="0">
-        <v>52793</v>
+        <v>715362</v>
       </c>
       <c r="G18" s="0">
-        <v>2.7599999999999998</v>
+        <v>3.79</v>
       </c>
       <c r="H18" s="0">
-        <v>5.2699999999999996</v>
+        <v>7.7599999999999998</v>
       </c>
       <c r="I18" s="0">
-        <v>73.060000000000002</v>
+        <v>78.930000000000007</v>
       </c>
       <c r="J18" s="0">
-        <v>641</v>
+        <v>752</v>
       </c>
       <c r="K18" s="0">
-        <v>887</v>
+        <v>4236.2399999999998</v>
       </c>
       <c r="L18" s="0">
-        <v>11.67</v>
+        <v>29.960000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="19">
@@ -927,40 +966,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>6650609757</v>
+        <v>121489743012</v>
       </c>
       <c r="C19" s="0">
-        <v>8369783759</v>
+        <v>159386624744</v>
       </c>
       <c r="D19" s="0">
-        <v>228495</v>
+        <v>559487</v>
       </c>
       <c r="E19" s="0">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="F19" s="0">
-        <v>166700</v>
+        <v>915873</v>
       </c>
       <c r="G19" s="0">
-        <v>4.5499999999999998</v>
+        <v>3.21</v>
       </c>
       <c r="H19" s="0">
-        <v>9.2100000000000009</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="I19" s="0">
-        <v>79.459999999999994</v>
+        <v>76.219999999999999</v>
       </c>
       <c r="J19" s="0">
-        <v>664</v>
+        <v>1024</v>
       </c>
       <c r="K19" s="0">
-        <v>1199</v>
+        <v>4697.8699999999999</v>
       </c>
       <c r="L19" s="0">
-        <v>15.84</v>
+        <v>27.609999999999999</v>
       </c>
       <c r="M19" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="20">
@@ -968,40 +1007,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1149052159</v>
+        <v>16184520330</v>
       </c>
       <c r="C20" s="0">
-        <v>1488703295</v>
+        <v>20867478445</v>
       </c>
       <c r="D20" s="0">
-        <v>76698</v>
+        <v>524968</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="F20" s="0">
-        <v>98988</v>
+        <v>113589</v>
       </c>
       <c r="G20" s="0">
-        <v>5.0999999999999996</v>
+        <v>2.8599999999999999</v>
       </c>
       <c r="H20" s="0">
-        <v>7.2599999999999998</v>
+        <v>7.75</v>
       </c>
       <c r="I20" s="0">
-        <v>77.180000000000007</v>
+        <v>77.560000000000002</v>
       </c>
       <c r="J20" s="0">
-        <v>301</v>
+        <v>1060</v>
       </c>
       <c r="K20" s="0">
-        <v>1672</v>
+        <v>4442.3800000000001</v>
       </c>
       <c r="L20" s="0">
-        <v>33.439999999999998</v>
+        <v>25.629999999999999</v>
       </c>
       <c r="M20" s="0">
-        <v>0.16</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1048,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>5269548743</v>
+        <v>1440587229</v>
       </c>
       <c r="C21" s="0">
-        <v>6710699855</v>
+        <v>1880841971</v>
       </c>
       <c r="D21" s="0">
-        <v>141397</v>
+        <v>563126</v>
       </c>
       <c r="E21" s="0">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="F21" s="0">
-        <v>222697</v>
+        <v>10559</v>
       </c>
       <c r="G21" s="0">
-        <v>4.6900000000000004</v>
+        <v>3.1600000000000001</v>
       </c>
       <c r="H21" s="0">
-        <v>7.6399999999999997</v>
+        <v>8.5600000000000005</v>
       </c>
       <c r="I21" s="0">
-        <v>78.519999999999996</v>
+        <v>76.590000000000003</v>
       </c>
       <c r="J21" s="0">
-        <v>422</v>
+        <v>1001</v>
       </c>
       <c r="K21" s="0">
-        <v>1832</v>
+        <v>4423.96</v>
       </c>
       <c r="L21" s="0">
-        <v>25.66</v>
+        <v>24.859999999999999</v>
       </c>
       <c r="M21" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="22">
@@ -1050,40 +1089,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>10070039543</v>
+        <v>61646356697</v>
       </c>
       <c r="C22" s="0">
-        <v>13725688928</v>
+        <v>81628279523</v>
       </c>
       <c r="D22" s="0">
-        <v>166918</v>
+        <v>642793</v>
       </c>
       <c r="E22" s="0">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="F22" s="0">
-        <v>332278</v>
+        <v>371593</v>
       </c>
       <c r="G22" s="0">
-        <v>4.04</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="H22" s="0">
-        <v>7.6100000000000003</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="I22" s="0">
-        <v>73.370000000000005</v>
+        <v>75.519999999999996</v>
       </c>
       <c r="J22" s="0">
-        <v>556</v>
+        <v>1227</v>
       </c>
       <c r="K22" s="0">
-        <v>1341</v>
+        <v>4562.8000000000002</v>
       </c>
       <c r="L22" s="0">
-        <v>18.059999999999999</v>
+        <v>25.48</v>
       </c>
       <c r="M22" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1091,40 +1130,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>20006870329</v>
+        <v>6110662648</v>
       </c>
       <c r="C23" s="0">
-        <v>27037438225</v>
+        <v>7446208119</v>
       </c>
       <c r="D23" s="0">
-        <v>129931</v>
+        <v>596174</v>
       </c>
       <c r="E23" s="0">
-        <v>65</v>
+        <v>179</v>
       </c>
       <c r="F23" s="0">
-        <v>757422</v>
+        <v>31603</v>
       </c>
       <c r="G23" s="0">
-        <v>3.6400000000000001</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H23" s="0">
-        <v>6.4100000000000001</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="I23" s="0">
-        <v>74</v>
+        <v>82.060000000000002</v>
       </c>
       <c r="J23" s="0">
-        <v>532</v>
+        <v>1317</v>
       </c>
       <c r="K23" s="0">
-        <v>1826</v>
+        <v>4038.4299999999998</v>
       </c>
       <c r="L23" s="0">
-        <v>27.460000000000001</v>
+        <v>22.579999999999998</v>
       </c>
       <c r="M23" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1132,40 +1171,573 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
+        <v>18861731702</v>
+      </c>
+      <c r="C24" s="0">
+        <v>26093310801</v>
+      </c>
+      <c r="D24" s="0">
+        <v>515882</v>
+      </c>
+      <c r="E24" s="0">
+        <v>186</v>
+      </c>
+      <c r="F24" s="0">
+        <v>100671</v>
+      </c>
+      <c r="G24" s="0">
+        <v>1.99</v>
+      </c>
+      <c r="H24" s="0">
+        <v>6.7599999999999998</v>
+      </c>
+      <c r="I24" s="0">
+        <v>72.290000000000006</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1399</v>
+      </c>
+      <c r="K24" s="0">
+        <v>5730.1000000000004</v>
+      </c>
+      <c r="L24" s="0">
+        <v>30.93</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.074999999999999997</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>8141345162</v>
+      </c>
+      <c r="C25" s="0">
+        <v>10413787531</v>
+      </c>
+      <c r="D25" s="0">
+        <v>775990</v>
+      </c>
+      <c r="E25" s="0">
+        <v>234</v>
+      </c>
+      <c r="F25" s="0">
+        <v>31591</v>
+      </c>
+      <c r="G25" s="0">
+        <v>2.3500000000000001</v>
+      </c>
+      <c r="H25" s="0">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="I25" s="0">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1409</v>
+      </c>
+      <c r="K25" s="0">
+        <v>6154.2600000000002</v>
+      </c>
+      <c r="L25" s="0">
+        <v>26.300000000000001</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>12826273084</v>
+      </c>
+      <c r="C26" s="0">
+        <v>17349402679</v>
+      </c>
+      <c r="D26" s="0">
+        <v>630200</v>
+      </c>
+      <c r="E26" s="0">
+        <v>210</v>
+      </c>
+      <c r="F26" s="0">
+        <v>35343</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1.28</v>
+      </c>
+      <c r="H26" s="0">
+        <v>6.7599999999999998</v>
+      </c>
+      <c r="I26" s="0">
+        <v>73.930000000000007</v>
+      </c>
+      <c r="J26" s="0">
+        <v>2379</v>
+      </c>
+      <c r="K26" s="0">
+        <v>7581.1999999999998</v>
+      </c>
+      <c r="L26" s="0">
+        <v>36.68</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.081000000000000003</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>7118188954</v>
+      </c>
+      <c r="C27" s="0">
+        <v>9596172675</v>
+      </c>
+      <c r="D27" s="0">
+        <v>803027</v>
+      </c>
+      <c r="E27" s="0">
+        <v>236</v>
+      </c>
+      <c r="F27" s="0">
+        <v>17007</v>
+      </c>
+      <c r="G27" s="0">
+        <v>1.4199999999999999</v>
+      </c>
+      <c r="H27" s="0">
+        <v>7.4800000000000004</v>
+      </c>
+      <c r="I27" s="0">
+        <v>74.180000000000007</v>
+      </c>
+      <c r="J27" s="0">
+        <v>2390</v>
+      </c>
+      <c r="K27" s="0">
+        <v>6796.04</v>
+      </c>
+      <c r="L27" s="0">
+        <v>28.780000000000001</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>8398335831</v>
+      </c>
+      <c r="C28" s="0">
+        <v>11804294822</v>
+      </c>
+      <c r="D28" s="0">
+        <v>923654</v>
+      </c>
+      <c r="E28" s="0">
+        <v>258</v>
+      </c>
+      <c r="F28" s="0">
+        <v>15817</v>
+      </c>
+      <c r="G28" s="0">
+        <v>1.24</v>
+      </c>
+      <c r="H28" s="0">
+        <v>7.6399999999999997</v>
+      </c>
+      <c r="I28" s="0">
+        <v>71.150000000000006</v>
+      </c>
+      <c r="J28" s="0">
+        <v>2874</v>
+      </c>
+      <c r="K28" s="0">
+        <v>8857.8799999999992</v>
+      </c>
+      <c r="L28" s="0">
+        <v>34.140000000000001</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.072999999999999995</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>9183762268</v>
+      </c>
+      <c r="C29" s="0">
+        <v>15211539946</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1363041</v>
+      </c>
+      <c r="E29" s="0">
+        <v>291</v>
+      </c>
+      <c r="F29" s="0">
+        <v>15724</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.4099999999999999</v>
+      </c>
+      <c r="H29" s="0">
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="I29" s="0">
+        <v>60.369999999999997</v>
+      </c>
+      <c r="J29" s="0">
+        <v>3326</v>
+      </c>
+      <c r="K29" s="0">
+        <v>7911.8699999999999</v>
+      </c>
+      <c r="L29" s="0">
+        <v>27.199999999999999</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.057000000000000002</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>2901906828</v>
+      </c>
+      <c r="C30" s="0">
+        <v>5703460033</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1584294</v>
+      </c>
+      <c r="E30" s="0">
+        <v>280</v>
+      </c>
+      <c r="F30" s="0">
+        <v>4652</v>
+      </c>
+      <c r="G30" s="0">
+        <v>1.29</v>
+      </c>
+      <c r="H30" s="0">
+        <v>11.539999999999999</v>
+      </c>
+      <c r="I30" s="0">
+        <v>50.880000000000003</v>
+      </c>
+      <c r="J30" s="0">
+        <v>4385</v>
+      </c>
+      <c r="K30" s="0">
+        <v>7883.3800000000001</v>
+      </c>
+      <c r="L30" s="0">
+        <v>28.190000000000001</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.057000000000000002</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>3381554723</v>
+      </c>
+      <c r="C31" s="0">
+        <v>9377588714</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1502819</v>
+      </c>
+      <c r="E31" s="0">
+        <v>303</v>
+      </c>
+      <c r="F31" s="0">
+        <v>5796</v>
+      </c>
+      <c r="G31" s="0">
+        <v>0.93000000000000005</v>
+      </c>
+      <c r="H31" s="0">
+        <v>9.6899999999999995</v>
+      </c>
+      <c r="I31" s="0">
+        <v>36.060000000000002</v>
+      </c>
+      <c r="J31" s="0">
+        <v>5341</v>
+      </c>
+      <c r="K31" s="0">
+        <v>8668.5300000000007</v>
+      </c>
+      <c r="L31" s="0">
+        <v>28.609999999999999</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.056000000000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>7835936452</v>
+      </c>
+      <c r="C32" s="0">
+        <v>12581643851</v>
+      </c>
+      <c r="D32" s="0">
+        <v>970057</v>
+      </c>
+      <c r="E32" s="0">
+        <v>232</v>
+      </c>
+      <c r="F32" s="0">
+        <v>18502</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="H32" s="0">
+        <v>8.8499999999999996</v>
+      </c>
+      <c r="I32" s="0">
+        <v>62.280000000000001</v>
+      </c>
+      <c r="J32" s="0">
+        <v>2996</v>
+      </c>
+      <c r="K32" s="0">
+        <v>9788.7099999999991</v>
+      </c>
+      <c r="L32" s="0">
+        <v>43.090000000000003</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.088999999999999996</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>14099923633</v>
+      </c>
+      <c r="C33" s="0">
+        <v>29148468899</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1342629</v>
+      </c>
+      <c r="E33" s="0">
+        <v>260</v>
+      </c>
+      <c r="F33" s="0">
+        <v>24680</v>
+      </c>
+      <c r="G33" s="0">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H33" s="0">
+        <v>10.359999999999999</v>
+      </c>
+      <c r="I33" s="0">
+        <v>48.369999999999997</v>
+      </c>
+      <c r="J33" s="0">
+        <v>4616</v>
+      </c>
+      <c r="K33" s="0">
+        <v>10128.32</v>
+      </c>
+      <c r="L33" s="0">
+        <v>39.579999999999998</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>4483167344</v>
+      </c>
+      <c r="C34" s="0">
+        <v>7695296310</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1626913</v>
+      </c>
+      <c r="E34" s="0">
+        <v>318</v>
+      </c>
+      <c r="F34" s="0">
+        <v>6255</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.3200000000000001</v>
+      </c>
+      <c r="H34" s="0">
+        <v>10.210000000000001</v>
+      </c>
+      <c r="I34" s="0">
+        <v>58.259999999999998</v>
+      </c>
+      <c r="J34" s="0">
+        <v>3869</v>
+      </c>
+      <c r="K34" s="0">
+        <v>7915.1300000000001</v>
+      </c>
+      <c r="L34" s="0">
+        <v>24.890000000000001</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>15501115262</v>
+      </c>
+      <c r="C35" s="0">
+        <v>23485493926</v>
+      </c>
+      <c r="D35" s="0">
+        <v>607174</v>
+      </c>
+      <c r="E35" s="0">
+        <v>272</v>
+      </c>
+      <c r="F35" s="0">
+        <v>32175</v>
+      </c>
+      <c r="G35" s="0">
+        <v>0.82999999999999996</v>
+      </c>
+      <c r="H35" s="0">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="I35" s="0">
+        <v>66</v>
+      </c>
+      <c r="J35" s="0">
+        <v>2714</v>
+      </c>
+      <c r="K35" s="0">
+        <v>13830.23</v>
+      </c>
+      <c r="L35" s="0">
+        <v>51.350000000000001</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
+        <v>11801825315</v>
+      </c>
+      <c r="C36" s="0">
+        <v>19558130434</v>
+      </c>
+      <c r="D36" s="0">
+        <v>1273316</v>
+      </c>
+      <c r="E36" s="0">
+        <v>320</v>
+      </c>
+      <c r="F36" s="0">
+        <v>16704</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="H36" s="0">
+        <v>8.0999999999999996</v>
+      </c>
+      <c r="I36" s="0">
+        <v>60.340000000000003</v>
+      </c>
+      <c r="J36" s="0">
+        <v>3652</v>
+      </c>
+      <c r="K36" s="0">
+        <v>14148.139999999999</v>
+      </c>
+      <c r="L36" s="0">
+        <v>44.170000000000002</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.089999999999999997</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
         <v>685497794958</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C37" s="0">
         <v>929802884475</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D37" s="0">
         <v>426163</v>
       </c>
-      <c r="E24" s="0">
+      <c r="E37" s="0">
         <v>133</v>
       </c>
-      <c r="F24" s="0">
+      <c r="F37" s="0">
         <v>6655805</v>
       </c>
-      <c r="G24" s="0">
+      <c r="G37" s="0">
         <v>3.0499999999999998</v>
       </c>
-      <c r="H24" s="0">
+      <c r="H37" s="0">
         <v>7.3600000000000003</v>
       </c>
-      <c r="I24" s="0">
+      <c r="I37" s="0">
         <v>73.730000000000004</v>
       </c>
-      <c r="J24" s="0">
+      <c r="J37" s="0">
         <v>886</v>
       </c>
-      <c r="K24" s="0">
-        <v>4378</v>
-      </c>
-      <c r="L24" s="0">
+      <c r="K37" s="0">
+        <v>4378.2799999999997</v>
+      </c>
+      <c r="L37" s="0">
         <v>29.27</v>
       </c>
-      <c r="M24" s="0">
-        <v>0.080000000000000002</v>
+      <c r="M37" s="0">
+        <v>0.075999999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Aircraft_Cumulative_Statistics_2021.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Aircraft_Cumulative_Statistics_2021.xlsx
@@ -13,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="51">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,7 +33,10 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>Q400</t>
+  </si>
+  <si>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -205,7 +211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -228,40 +234,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
@@ -269,40 +275,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>3562562849</v>
+        <v>37931824</v>
       </c>
       <c r="C2" s="0">
-        <v>4655109479</v>
+        <v>62273728</v>
       </c>
       <c r="D2" s="0">
-        <v>48842</v>
+        <v>23589</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F2" s="0">
-        <v>280413</v>
+        <v>4960</v>
       </c>
       <c r="G2" s="0">
-        <v>2.9399999999999999</v>
+        <v>1.8799999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>4.2199999999999998</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="I2" s="0">
-        <v>76.530000000000001</v>
+        <v>60.909999999999997</v>
       </c>
       <c r="J2" s="0">
-        <v>332</v>
+        <v>285</v>
       </c>
       <c r="K2" s="0">
-        <v>1588.6700000000001</v>
+        <v>1551.46</v>
       </c>
       <c r="L2" s="0">
-        <v>31.780000000000001</v>
+        <v>35.259999999999998</v>
       </c>
       <c r="M2" s="0">
-        <v>0.13700000000000001</v>
+        <v>0.16200000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -310,40 +316,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>3589076503</v>
+        <v>3562562849</v>
       </c>
       <c r="C3" s="0">
-        <v>5144234346</v>
+        <v>4655109479</v>
       </c>
       <c r="D3" s="0">
-        <v>56117</v>
+        <v>48842</v>
       </c>
       <c r="E3" s="0">
         <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>288283</v>
+        <v>280413</v>
       </c>
       <c r="G3" s="0">
-        <v>3.1400000000000001</v>
+        <v>2.9399999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>4.3300000000000001</v>
+        <v>4.2199999999999998</v>
       </c>
       <c r="I3" s="0">
-        <v>69.769999999999996</v>
+        <v>76.530000000000001</v>
       </c>
       <c r="J3" s="0">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="K3" s="0">
-        <v>2296.3499999999999</v>
+        <v>1588.6700000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>45.93</v>
+        <v>31.780000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.17699999999999999</v>
+        <v>0.13700000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -351,40 +357,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>1598831898</v>
+        <v>3589076503</v>
       </c>
       <c r="C4" s="0">
-        <v>2014598782</v>
+        <v>5144234346</v>
       </c>
       <c r="D4" s="0">
-        <v>89737</v>
+        <v>56117</v>
       </c>
       <c r="E4" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F4" s="0">
-        <v>48856</v>
+        <v>288283</v>
       </c>
       <c r="G4" s="0">
-        <v>2.1800000000000002</v>
+        <v>3.1400000000000001</v>
       </c>
       <c r="H4" s="0">
-        <v>4.3200000000000003</v>
+        <v>4.3300000000000001</v>
       </c>
       <c r="I4" s="0">
-        <v>79.359999999999999</v>
+        <v>69.769999999999996</v>
       </c>
       <c r="J4" s="0">
-        <v>591</v>
+        <v>357</v>
       </c>
       <c r="K4" s="0">
-        <v>1299.4100000000001</v>
+        <v>2296.3499999999999</v>
       </c>
       <c r="L4" s="0">
-        <v>18.620000000000001</v>
+        <v>45.93</v>
       </c>
       <c r="M4" s="0">
-        <v>0.063</v>
+        <v>0.17699999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -392,40 +398,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>31383781010</v>
+        <v>1598831898</v>
       </c>
       <c r="C5" s="0">
-        <v>41540640374</v>
+        <v>2014598782</v>
       </c>
       <c r="D5" s="0">
-        <v>142800</v>
+        <v>89737</v>
       </c>
       <c r="E5" s="0">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F5" s="0">
-        <v>906234</v>
+        <v>48856</v>
       </c>
       <c r="G5" s="0">
-        <v>3.1200000000000001</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>6.0700000000000003</v>
+        <v>4.3200000000000003</v>
       </c>
       <c r="I5" s="0">
-        <v>75.549999999999997</v>
+        <v>79.359999999999999</v>
       </c>
       <c r="J5" s="0">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="K5" s="0">
-        <v>1379.3800000000001</v>
+        <v>1299.4100000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>18.48</v>
+        <v>18.620000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.058999999999999997</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="6">
@@ -433,40 +439,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>1004554080</v>
+        <v>31383781010</v>
       </c>
       <c r="C6" s="0">
-        <v>1241697900</v>
+        <v>41540640374</v>
       </c>
       <c r="D6" s="0">
-        <v>69137</v>
+        <v>142800</v>
       </c>
       <c r="E6" s="0">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F6" s="0">
-        <v>59901</v>
+        <v>906234</v>
       </c>
       <c r="G6" s="0">
-        <v>3.3399999999999999</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>5.3499999999999996</v>
+        <v>6.0700000000000003</v>
       </c>
       <c r="I6" s="0">
-        <v>80.900000000000006</v>
+        <v>75.549999999999997</v>
       </c>
       <c r="J6" s="0">
-        <v>415</v>
+        <v>614</v>
       </c>
       <c r="K6" s="0">
-        <v>2045.0999999999999</v>
+        <v>1379.3800000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>40.899999999999999</v>
+        <v>18.48</v>
       </c>
       <c r="M6" s="0">
-        <v>0.158</v>
+        <v>0.058999999999999997</v>
       </c>
     </row>
     <row r="7">
@@ -474,40 +480,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>6714160960</v>
+        <v>930652685</v>
       </c>
       <c r="C7" s="0">
-        <v>8944331084</v>
+        <v>1335334896</v>
       </c>
       <c r="D7" s="0">
-        <v>117813</v>
+        <v>65618</v>
       </c>
       <c r="E7" s="0">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F7" s="0">
-        <v>274585</v>
+        <v>57961</v>
       </c>
       <c r="G7" s="0">
-        <v>3.6200000000000001</v>
+        <v>2.8500000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>6.2300000000000004</v>
+        <v>3.7000000000000002</v>
       </c>
       <c r="I7" s="0">
-        <v>75.069999999999993</v>
+        <v>69.689999999999998</v>
       </c>
       <c r="J7" s="0">
-        <v>495</v>
+        <v>303</v>
       </c>
       <c r="K7" s="0">
-        <v>1944.04</v>
+        <v>2046.51</v>
       </c>
       <c r="L7" s="0">
-        <v>29.539999999999999</v>
+        <v>26.93</v>
       </c>
       <c r="M7" s="0">
-        <v>0.10299999999999999</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="8">
@@ -515,40 +521,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>3549912290</v>
+        <v>1004554080</v>
       </c>
       <c r="C8" s="0">
-        <v>4709209138</v>
+        <v>1241697900</v>
       </c>
       <c r="D8" s="0">
-        <v>215032</v>
+        <v>69137</v>
       </c>
       <c r="E8" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F8" s="0">
-        <v>73074</v>
+        <v>59901</v>
       </c>
       <c r="G8" s="0">
         <v>3.3399999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>6.5300000000000002</v>
+        <v>5.3499999999999996</v>
       </c>
       <c r="I8" s="0">
-        <v>75.379999999999995</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="J8" s="0">
-        <v>642</v>
+        <v>415</v>
       </c>
       <c r="K8" s="0">
-        <v>4575.6700000000001</v>
+        <v>2045.0999999999999</v>
       </c>
       <c r="L8" s="0">
-        <v>45.619999999999997</v>
+        <v>40.899999999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>0.13900000000000001</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="9">
@@ -556,40 +562,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>12010167044</v>
+        <v>6714160960</v>
       </c>
       <c r="C9" s="0">
-        <v>15999576473</v>
+        <v>8944331084</v>
       </c>
       <c r="D9" s="0">
-        <v>161743</v>
+        <v>117813</v>
       </c>
       <c r="E9" s="0">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F9" s="0">
-        <v>446531</v>
+        <v>274585</v>
       </c>
       <c r="G9" s="0">
-        <v>4.5099999999999998</v>
+        <v>3.6200000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>7.4100000000000001</v>
+        <v>6.2300000000000004</v>
       </c>
       <c r="I9" s="0">
         <v>75.069999999999993</v>
       </c>
       <c r="J9" s="0">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="K9" s="0">
-        <v>1513.45</v>
+        <v>1944.04</v>
       </c>
       <c r="L9" s="0">
-        <v>20.030000000000001</v>
+        <v>29.539999999999999</v>
       </c>
       <c r="M9" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -597,40 +603,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>3319238941</v>
+        <v>3549912290</v>
       </c>
       <c r="C10" s="0">
-        <v>4353176458</v>
+        <v>4709209138</v>
       </c>
       <c r="D10" s="0">
-        <v>296740</v>
+        <v>215032</v>
       </c>
       <c r="E10" s="0">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="F10" s="0">
-        <v>40951</v>
+        <v>73074</v>
       </c>
       <c r="G10" s="0">
-        <v>2.79</v>
+        <v>3.3399999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>7.29</v>
+        <v>6.5300000000000002</v>
       </c>
       <c r="I10" s="0">
-        <v>76.25</v>
+        <v>75.379999999999995</v>
       </c>
       <c r="J10" s="0">
-        <v>975</v>
+        <v>642</v>
       </c>
       <c r="K10" s="0">
-        <v>4416.4200000000001</v>
+        <v>4575.6700000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>40.530000000000001</v>
+        <v>45.619999999999997</v>
       </c>
       <c r="M10" s="0">
-        <v>0.108</v>
+        <v>0.13900000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -638,40 +644,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>1187889565</v>
+        <v>12010167044</v>
       </c>
       <c r="C11" s="0">
-        <v>1558931519</v>
+        <v>15999576473</v>
       </c>
       <c r="D11" s="0">
-        <v>385874</v>
+        <v>161743</v>
       </c>
       <c r="E11" s="0">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="F11" s="0">
-        <v>11756</v>
+        <v>446531</v>
       </c>
       <c r="G11" s="0">
-        <v>2.9100000000000001</v>
+        <v>4.5099999999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>7.9000000000000004</v>
+        <v>7.4100000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>76.200000000000003</v>
+        <v>75.069999999999993</v>
       </c>
       <c r="J11" s="0">
-        <v>1000</v>
+        <v>474</v>
       </c>
       <c r="K11" s="0">
-        <v>4434.75</v>
+        <v>1513.45</v>
       </c>
       <c r="L11" s="0">
-        <v>33.460000000000001</v>
+        <v>20.030000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="12">
@@ -679,40 +685,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>29748111048</v>
+        <v>3319238941</v>
       </c>
       <c r="C12" s="0">
-        <v>38967063060</v>
+        <v>4353176458</v>
       </c>
       <c r="D12" s="0">
-        <v>329922</v>
+        <v>296740</v>
       </c>
       <c r="E12" s="0">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F12" s="0">
-        <v>344929</v>
+        <v>40951</v>
       </c>
       <c r="G12" s="0">
-        <v>2.9199999999999999</v>
+        <v>2.79</v>
       </c>
       <c r="H12" s="0">
-        <v>6.8799999999999999</v>
+        <v>7.29</v>
       </c>
       <c r="I12" s="0">
-        <v>76.340000000000003</v>
+        <v>76.25</v>
       </c>
       <c r="J12" s="0">
-        <v>851</v>
+        <v>975</v>
       </c>
       <c r="K12" s="0">
-        <v>4431.6000000000004</v>
+        <v>4416.4200000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>33.450000000000003</v>
+        <v>40.530000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.091999999999999998</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="13">
@@ -720,40 +726,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>66054316806</v>
+        <v>1187889565</v>
       </c>
       <c r="C13" s="0">
-        <v>87801329700</v>
+        <v>1558931519</v>
       </c>
       <c r="D13" s="0">
-        <v>478195</v>
+        <v>385874</v>
       </c>
       <c r="E13" s="0">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="F13" s="0">
-        <v>540471</v>
+        <v>11756</v>
       </c>
       <c r="G13" s="0">
-        <v>2.9399999999999999</v>
+        <v>2.9100000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>7.7000000000000002</v>
+        <v>7.9000000000000004</v>
       </c>
       <c r="I13" s="0">
-        <v>75.230000000000004</v>
+        <v>76.200000000000003</v>
       </c>
       <c r="J13" s="0">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="K13" s="0">
-        <v>4896.0200000000004</v>
+        <v>4434.75</v>
       </c>
       <c r="L13" s="0">
-        <v>29.800000000000001</v>
+        <v>33.460000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -761,40 +767,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>21123211863</v>
+        <v>29748111048</v>
       </c>
       <c r="C14" s="0">
-        <v>27477820744</v>
+        <v>38967063060</v>
       </c>
       <c r="D14" s="0">
-        <v>670845</v>
+        <v>329922</v>
       </c>
       <c r="E14" s="0">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="F14" s="0">
-        <v>147702</v>
+        <v>344929</v>
       </c>
       <c r="G14" s="0">
-        <v>3.6099999999999999</v>
+        <v>2.9199999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>9.7899999999999991</v>
+        <v>6.8799999999999999</v>
       </c>
       <c r="I14" s="0">
-        <v>76.870000000000005</v>
+        <v>76.340000000000003</v>
       </c>
       <c r="J14" s="0">
-        <v>1009</v>
+        <v>851</v>
       </c>
       <c r="K14" s="0">
-        <v>4174.4300000000003</v>
+        <v>4431.6000000000004</v>
       </c>
       <c r="L14" s="0">
-        <v>22.629999999999999</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="M14" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="15">
@@ -802,40 +808,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>87086883349</v>
+        <v>66054316806</v>
       </c>
       <c r="C15" s="0">
-        <v>110394550101</v>
+        <v>87801329700</v>
       </c>
       <c r="D15" s="0">
-        <v>669301</v>
+        <v>478195</v>
       </c>
       <c r="E15" s="0">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="F15" s="0">
-        <v>512547</v>
+        <v>540471</v>
       </c>
       <c r="G15" s="0">
-        <v>3.1099999999999999</v>
+        <v>2.9399999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>9.1699999999999999</v>
+        <v>7.7000000000000002</v>
       </c>
       <c r="I15" s="0">
-        <v>78.890000000000001</v>
+        <v>75.230000000000004</v>
       </c>
       <c r="J15" s="0">
-        <v>1148</v>
+        <v>988</v>
       </c>
       <c r="K15" s="0">
-        <v>5336.0200000000004</v>
+        <v>4896.0200000000004</v>
       </c>
       <c r="L15" s="0">
-        <v>28.309999999999999</v>
+        <v>29.800000000000001</v>
       </c>
       <c r="M15" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -843,40 +849,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>18350821703</v>
+        <v>21123211863</v>
       </c>
       <c r="C16" s="0">
-        <v>24523726632</v>
+        <v>27477820744</v>
       </c>
       <c r="D16" s="0">
-        <v>879617</v>
+        <v>670845</v>
       </c>
       <c r="E16" s="0">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F16" s="0">
-        <v>68317</v>
+        <v>147702</v>
       </c>
       <c r="G16" s="0">
-        <v>2.4500000000000002</v>
+        <v>3.6099999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>10.59</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="I16" s="0">
-        <v>74.829999999999998</v>
+        <v>76.870000000000005</v>
       </c>
       <c r="J16" s="0">
-        <v>1857</v>
+        <v>1009</v>
       </c>
       <c r="K16" s="0">
-        <v>5318.9099999999999</v>
+        <v>4174.4300000000003</v>
       </c>
       <c r="L16" s="0">
-        <v>27.489999999999998</v>
+        <v>22.629999999999999</v>
       </c>
       <c r="M16" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -884,40 +890,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>3741015240</v>
+        <v>87086883349</v>
       </c>
       <c r="C17" s="0">
-        <v>5152156687</v>
+        <v>110394550101</v>
       </c>
       <c r="D17" s="0">
-        <v>200239</v>
+        <v>669301</v>
       </c>
       <c r="E17" s="0">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="F17" s="0">
-        <v>127759</v>
+        <v>512547</v>
       </c>
       <c r="G17" s="0">
-        <v>4.9699999999999998</v>
+        <v>3.1099999999999999</v>
       </c>
       <c r="H17" s="0">
-        <v>6.2400000000000002</v>
+        <v>9.1699999999999999</v>
       </c>
       <c r="I17" s="0">
-        <v>72.609999999999999</v>
+        <v>78.890000000000001</v>
       </c>
       <c r="J17" s="0">
-        <v>360</v>
+        <v>1148</v>
       </c>
       <c r="K17" s="0">
-        <v>4668.29</v>
+        <v>5336.0200000000004</v>
       </c>
       <c r="L17" s="0">
-        <v>41.229999999999997</v>
+        <v>28.309999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.14499999999999999</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="18">
@@ -925,40 +931,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>60066323335</v>
+        <v>18350821703</v>
       </c>
       <c r="C18" s="0">
-        <v>76096708575</v>
+        <v>24523726632</v>
       </c>
       <c r="D18" s="0">
-        <v>403332</v>
+        <v>879617</v>
       </c>
       <c r="E18" s="0">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="F18" s="0">
-        <v>715362</v>
+        <v>68317</v>
       </c>
       <c r="G18" s="0">
-        <v>3.79</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H18" s="0">
-        <v>7.7599999999999998</v>
+        <v>10.59</v>
       </c>
       <c r="I18" s="0">
-        <v>78.930000000000007</v>
+        <v>74.829999999999998</v>
       </c>
       <c r="J18" s="0">
-        <v>752</v>
+        <v>1857</v>
       </c>
       <c r="K18" s="0">
-        <v>4236.2399999999998</v>
+        <v>5318.9099999999999</v>
       </c>
       <c r="L18" s="0">
-        <v>29.960000000000001</v>
+        <v>27.489999999999998</v>
       </c>
       <c r="M18" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -966,40 +972,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>121489743012</v>
+        <v>3741015240</v>
       </c>
       <c r="C19" s="0">
-        <v>159386624744</v>
+        <v>5152156687</v>
       </c>
       <c r="D19" s="0">
-        <v>559487</v>
+        <v>200239</v>
       </c>
       <c r="E19" s="0">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="F19" s="0">
-        <v>915873</v>
+        <v>127759</v>
       </c>
       <c r="G19" s="0">
-        <v>3.21</v>
+        <v>4.9699999999999998</v>
       </c>
       <c r="H19" s="0">
-        <v>8.5299999999999994</v>
+        <v>6.2400000000000002</v>
       </c>
       <c r="I19" s="0">
-        <v>76.219999999999999</v>
+        <v>72.609999999999999</v>
       </c>
       <c r="J19" s="0">
-        <v>1024</v>
+        <v>360</v>
       </c>
       <c r="K19" s="0">
-        <v>4697.8699999999999</v>
+        <v>4668.29</v>
       </c>
       <c r="L19" s="0">
-        <v>27.609999999999999</v>
+        <v>41.229999999999997</v>
       </c>
       <c r="M19" s="0">
-        <v>0.071999999999999995</v>
+        <v>0.14499999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1007,40 +1013,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>16184520330</v>
+        <v>60131029150</v>
       </c>
       <c r="C20" s="0">
-        <v>20867478445</v>
+        <v>76187565600</v>
       </c>
       <c r="D20" s="0">
-        <v>524968</v>
+        <v>403814</v>
       </c>
       <c r="E20" s="0">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="F20" s="0">
-        <v>113589</v>
+        <v>716071</v>
       </c>
       <c r="G20" s="0">
-        <v>2.8599999999999999</v>
+        <v>3.7999999999999998</v>
       </c>
       <c r="H20" s="0">
-        <v>7.75</v>
+        <v>7.7699999999999996</v>
       </c>
       <c r="I20" s="0">
-        <v>77.560000000000002</v>
+        <v>78.920000000000002</v>
       </c>
       <c r="J20" s="0">
-        <v>1060</v>
+        <v>753</v>
       </c>
       <c r="K20" s="0">
-        <v>4442.3800000000001</v>
+        <v>4231.2600000000002</v>
       </c>
       <c r="L20" s="0">
-        <v>25.629999999999999</v>
+        <v>29.920000000000002</v>
       </c>
       <c r="M20" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -1048,40 +1054,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>1440587229</v>
+        <v>121649794708</v>
       </c>
       <c r="C21" s="0">
-        <v>1880841971</v>
+        <v>159663333974</v>
       </c>
       <c r="D21" s="0">
-        <v>563126</v>
+        <v>560458</v>
       </c>
       <c r="E21" s="0">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F21" s="0">
-        <v>10559</v>
+        <v>918296</v>
       </c>
       <c r="G21" s="0">
-        <v>3.1600000000000001</v>
+        <v>3.2200000000000002</v>
       </c>
       <c r="H21" s="0">
-        <v>8.5600000000000005</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="I21" s="0">
-        <v>76.590000000000003</v>
+        <v>76.189999999999998</v>
       </c>
       <c r="J21" s="0">
-        <v>1001</v>
+        <v>1023</v>
       </c>
       <c r="K21" s="0">
-        <v>4423.96</v>
+        <v>4689.5900000000001</v>
       </c>
       <c r="L21" s="0">
-        <v>24.859999999999999</v>
+        <v>27.559999999999999</v>
       </c>
       <c r="M21" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="22">
@@ -1089,40 +1095,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>61646356697</v>
+        <v>16184520330</v>
       </c>
       <c r="C22" s="0">
-        <v>81628279523</v>
+        <v>20867478445</v>
       </c>
       <c r="D22" s="0">
-        <v>642793</v>
+        <v>524968</v>
       </c>
       <c r="E22" s="0">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F22" s="0">
-        <v>371593</v>
+        <v>113589</v>
       </c>
       <c r="G22" s="0">
-        <v>2.9300000000000002</v>
+        <v>2.8599999999999999</v>
       </c>
       <c r="H22" s="0">
-        <v>9.0299999999999994</v>
+        <v>7.75</v>
       </c>
       <c r="I22" s="0">
-        <v>75.519999999999996</v>
+        <v>77.560000000000002</v>
       </c>
       <c r="J22" s="0">
-        <v>1227</v>
+        <v>1060</v>
       </c>
       <c r="K22" s="0">
-        <v>4562.8000000000002</v>
+        <v>4442.3800000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>25.48</v>
+        <v>25.629999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="23">
@@ -1130,40 +1136,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>6110662648</v>
+        <v>1440587229</v>
       </c>
       <c r="C23" s="0">
-        <v>7446208119</v>
+        <v>1880841971</v>
       </c>
       <c r="D23" s="0">
-        <v>596174</v>
+        <v>563126</v>
       </c>
       <c r="E23" s="0">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F23" s="0">
-        <v>31603</v>
+        <v>10559</v>
       </c>
       <c r="G23" s="0">
-        <v>2.5299999999999998</v>
+        <v>3.1600000000000001</v>
       </c>
       <c r="H23" s="0">
-        <v>8.3100000000000005</v>
+        <v>8.5600000000000005</v>
       </c>
       <c r="I23" s="0">
-        <v>82.060000000000002</v>
+        <v>76.590000000000003</v>
       </c>
       <c r="J23" s="0">
-        <v>1317</v>
+        <v>1001</v>
       </c>
       <c r="K23" s="0">
-        <v>4038.4299999999998</v>
+        <v>4423.96</v>
       </c>
       <c r="L23" s="0">
-        <v>22.579999999999998</v>
+        <v>24.859999999999999</v>
       </c>
       <c r="M23" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="24">
@@ -1171,40 +1177,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>18861731702</v>
+        <v>61646356697</v>
       </c>
       <c r="C24" s="0">
-        <v>26093310801</v>
+        <v>81628279523</v>
       </c>
       <c r="D24" s="0">
-        <v>515882</v>
+        <v>642793</v>
       </c>
       <c r="E24" s="0">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F24" s="0">
-        <v>100671</v>
+        <v>371593</v>
       </c>
       <c r="G24" s="0">
-        <v>1.99</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="H24" s="0">
-        <v>6.7599999999999998</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="I24" s="0">
-        <v>72.290000000000006</v>
+        <v>75.519999999999996</v>
       </c>
       <c r="J24" s="0">
-        <v>1399</v>
+        <v>1227</v>
       </c>
       <c r="K24" s="0">
-        <v>5730.1000000000004</v>
+        <v>4562.8000000000002</v>
       </c>
       <c r="L24" s="0">
-        <v>30.93</v>
+        <v>25.48</v>
       </c>
       <c r="M24" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1212,40 +1218,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>8141345162</v>
+        <v>6110662648</v>
       </c>
       <c r="C25" s="0">
-        <v>10413787531</v>
+        <v>7446208119</v>
       </c>
       <c r="D25" s="0">
-        <v>775990</v>
+        <v>596174</v>
       </c>
       <c r="E25" s="0">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="F25" s="0">
-        <v>31591</v>
+        <v>31603</v>
       </c>
       <c r="G25" s="0">
-        <v>2.3500000000000001</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H25" s="0">
-        <v>8.0399999999999991</v>
+        <v>8.3100000000000005</v>
       </c>
       <c r="I25" s="0">
-        <v>78.180000000000007</v>
+        <v>82.060000000000002</v>
       </c>
       <c r="J25" s="0">
-        <v>1409</v>
+        <v>1317</v>
       </c>
       <c r="K25" s="0">
-        <v>6154.2600000000002</v>
+        <v>4038.4299999999998</v>
       </c>
       <c r="L25" s="0">
-        <v>26.300000000000001</v>
+        <v>22.579999999999998</v>
       </c>
       <c r="M25" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1253,40 +1259,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>12826273084</v>
+        <v>18861731702</v>
       </c>
       <c r="C26" s="0">
-        <v>17349402679</v>
+        <v>26093310801</v>
       </c>
       <c r="D26" s="0">
-        <v>630200</v>
+        <v>515882</v>
       </c>
       <c r="E26" s="0">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="F26" s="0">
-        <v>35343</v>
+        <v>100671</v>
       </c>
       <c r="G26" s="0">
-        <v>1.28</v>
+        <v>1.99</v>
       </c>
       <c r="H26" s="0">
         <v>6.7599999999999998</v>
       </c>
       <c r="I26" s="0">
-        <v>73.930000000000007</v>
+        <v>72.290000000000006</v>
       </c>
       <c r="J26" s="0">
-        <v>2379</v>
+        <v>1399</v>
       </c>
       <c r="K26" s="0">
-        <v>7581.1999999999998</v>
+        <v>5730.1000000000004</v>
       </c>
       <c r="L26" s="0">
-        <v>36.68</v>
+        <v>30.93</v>
       </c>
       <c r="M26" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="27">
@@ -1294,40 +1300,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>7118188954</v>
+        <v>8141345162</v>
       </c>
       <c r="C27" s="0">
-        <v>9596172675</v>
+        <v>10413787531</v>
       </c>
       <c r="D27" s="0">
-        <v>803027</v>
+        <v>775990</v>
       </c>
       <c r="E27" s="0">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F27" s="0">
-        <v>17007</v>
+        <v>31591</v>
       </c>
       <c r="G27" s="0">
-        <v>1.4199999999999999</v>
+        <v>2.3500000000000001</v>
       </c>
       <c r="H27" s="0">
-        <v>7.4800000000000004</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="I27" s="0">
-        <v>74.180000000000007</v>
+        <v>78.180000000000007</v>
       </c>
       <c r="J27" s="0">
-        <v>2390</v>
+        <v>1409</v>
       </c>
       <c r="K27" s="0">
-        <v>6796.04</v>
+        <v>6154.2600000000002</v>
       </c>
       <c r="L27" s="0">
-        <v>28.780000000000001</v>
+        <v>26.300000000000001</v>
       </c>
       <c r="M27" s="0">
-        <v>0.063</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1335,40 +1341,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>8398335831</v>
+        <v>12826273084</v>
       </c>
       <c r="C28" s="0">
-        <v>11804294822</v>
+        <v>17349402679</v>
       </c>
       <c r="D28" s="0">
-        <v>923654</v>
+        <v>630200</v>
       </c>
       <c r="E28" s="0">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="F28" s="0">
-        <v>15817</v>
+        <v>35343</v>
       </c>
       <c r="G28" s="0">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="H28" s="0">
-        <v>7.6399999999999997</v>
+        <v>6.7599999999999998</v>
       </c>
       <c r="I28" s="0">
-        <v>71.150000000000006</v>
+        <v>73.930000000000007</v>
       </c>
       <c r="J28" s="0">
-        <v>2874</v>
+        <v>2379</v>
       </c>
       <c r="K28" s="0">
-        <v>8857.8799999999992</v>
+        <v>7581.1999999999998</v>
       </c>
       <c r="L28" s="0">
-        <v>34.140000000000001</v>
+        <v>36.68</v>
       </c>
       <c r="M28" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="29">
@@ -1376,40 +1382,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>9183762268</v>
+        <v>7118188954</v>
       </c>
       <c r="C29" s="0">
-        <v>15211539946</v>
+        <v>9596172675</v>
       </c>
       <c r="D29" s="0">
-        <v>1363041</v>
+        <v>803027</v>
       </c>
       <c r="E29" s="0">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="F29" s="0">
-        <v>15724</v>
+        <v>17007</v>
       </c>
       <c r="G29" s="0">
-        <v>1.4099999999999999</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="H29" s="0">
-        <v>9.8699999999999992</v>
+        <v>7.4800000000000004</v>
       </c>
       <c r="I29" s="0">
-        <v>60.369999999999997</v>
+        <v>74.180000000000007</v>
       </c>
       <c r="J29" s="0">
-        <v>3326</v>
+        <v>2390</v>
       </c>
       <c r="K29" s="0">
-        <v>7911.8699999999999</v>
+        <v>6796.04</v>
       </c>
       <c r="L29" s="0">
-        <v>27.199999999999999</v>
+        <v>28.780000000000001</v>
       </c>
       <c r="M29" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="30">
@@ -1417,40 +1423,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>2901906828</v>
+        <v>8398335831</v>
       </c>
       <c r="C30" s="0">
-        <v>5703460033</v>
+        <v>11804294822</v>
       </c>
       <c r="D30" s="0">
-        <v>1584294</v>
+        <v>923654</v>
       </c>
       <c r="E30" s="0">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="F30" s="0">
-        <v>4652</v>
+        <v>15817</v>
       </c>
       <c r="G30" s="0">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="H30" s="0">
-        <v>11.539999999999999</v>
+        <v>7.6399999999999997</v>
       </c>
       <c r="I30" s="0">
-        <v>50.880000000000003</v>
+        <v>71.150000000000006</v>
       </c>
       <c r="J30" s="0">
-        <v>4385</v>
+        <v>2874</v>
       </c>
       <c r="K30" s="0">
-        <v>7883.3800000000001</v>
+        <v>8857.8799999999992</v>
       </c>
       <c r="L30" s="0">
-        <v>28.190000000000001</v>
+        <v>34.140000000000001</v>
       </c>
       <c r="M30" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="31">
@@ -1458,40 +1464,40 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>3381554723</v>
+        <v>9183762268</v>
       </c>
       <c r="C31" s="0">
-        <v>9377588714</v>
+        <v>15211539946</v>
       </c>
       <c r="D31" s="0">
-        <v>1502819</v>
+        <v>1363041</v>
       </c>
       <c r="E31" s="0">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="F31" s="0">
-        <v>5796</v>
+        <v>15724</v>
       </c>
       <c r="G31" s="0">
-        <v>0.93000000000000005</v>
+        <v>1.4099999999999999</v>
       </c>
       <c r="H31" s="0">
-        <v>9.6899999999999995</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="I31" s="0">
-        <v>36.060000000000002</v>
+        <v>60.369999999999997</v>
       </c>
       <c r="J31" s="0">
-        <v>5341</v>
+        <v>3326</v>
       </c>
       <c r="K31" s="0">
-        <v>8668.5300000000007</v>
+        <v>7911.8699999999999</v>
       </c>
       <c r="L31" s="0">
-        <v>28.609999999999999</v>
+        <v>27.199999999999999</v>
       </c>
       <c r="M31" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="32">
@@ -1499,40 +1505,40 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>7835936452</v>
+        <v>2901906828</v>
       </c>
       <c r="C32" s="0">
-        <v>12581643851</v>
+        <v>5703460033</v>
       </c>
       <c r="D32" s="0">
-        <v>970057</v>
+        <v>1584294</v>
       </c>
       <c r="E32" s="0">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="F32" s="0">
-        <v>18502</v>
+        <v>4652</v>
       </c>
       <c r="G32" s="0">
-        <v>1.4299999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="H32" s="0">
-        <v>8.8499999999999996</v>
+        <v>11.539999999999999</v>
       </c>
       <c r="I32" s="0">
-        <v>62.280000000000001</v>
+        <v>50.880000000000003</v>
       </c>
       <c r="J32" s="0">
-        <v>2996</v>
+        <v>4385</v>
       </c>
       <c r="K32" s="0">
-        <v>9788.7099999999991</v>
+        <v>7883.3800000000001</v>
       </c>
       <c r="L32" s="0">
-        <v>43.090000000000003</v>
+        <v>28.190000000000001</v>
       </c>
       <c r="M32" s="0">
-        <v>0.088999999999999996</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="33">
@@ -1540,40 +1546,40 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>14099923633</v>
+        <v>3381554723</v>
       </c>
       <c r="C33" s="0">
-        <v>29148468899</v>
+        <v>9377588714</v>
       </c>
       <c r="D33" s="0">
-        <v>1342629</v>
+        <v>1502819</v>
       </c>
       <c r="E33" s="0">
-        <v>260</v>
+        <v>303</v>
       </c>
       <c r="F33" s="0">
-        <v>24680</v>
+        <v>5796</v>
       </c>
       <c r="G33" s="0">
-        <v>1.1399999999999999</v>
+        <v>0.93000000000000005</v>
       </c>
       <c r="H33" s="0">
-        <v>10.359999999999999</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="I33" s="0">
-        <v>48.369999999999997</v>
+        <v>36.060000000000002</v>
       </c>
       <c r="J33" s="0">
-        <v>4616</v>
+        <v>5341</v>
       </c>
       <c r="K33" s="0">
-        <v>10128.32</v>
+        <v>8668.5300000000007</v>
       </c>
       <c r="L33" s="0">
-        <v>39.579999999999998</v>
+        <v>28.609999999999999</v>
       </c>
       <c r="M33" s="0">
-        <v>0.078</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1581,40 +1587,40 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>4483167344</v>
+        <v>7835936452</v>
       </c>
       <c r="C34" s="0">
-        <v>7695296310</v>
+        <v>12581643851</v>
       </c>
       <c r="D34" s="0">
-        <v>1626913</v>
+        <v>970057</v>
       </c>
       <c r="E34" s="0">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="F34" s="0">
-        <v>6255</v>
+        <v>18502</v>
       </c>
       <c r="G34" s="0">
-        <v>1.3200000000000001</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H34" s="0">
-        <v>10.210000000000001</v>
+        <v>8.8499999999999996</v>
       </c>
       <c r="I34" s="0">
-        <v>58.259999999999998</v>
+        <v>62.280000000000001</v>
       </c>
       <c r="J34" s="0">
-        <v>3869</v>
+        <v>2996</v>
       </c>
       <c r="K34" s="0">
-        <v>7915.1300000000001</v>
+        <v>9788.7099999999991</v>
       </c>
       <c r="L34" s="0">
-        <v>24.890000000000001</v>
+        <v>43.090000000000003</v>
       </c>
       <c r="M34" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="35">
@@ -1622,40 +1628,40 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>15501115262</v>
+        <v>14099923633</v>
       </c>
       <c r="C35" s="0">
-        <v>23485493926</v>
+        <v>29148468899</v>
       </c>
       <c r="D35" s="0">
-        <v>607174</v>
+        <v>1342629</v>
       </c>
       <c r="E35" s="0">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="F35" s="0">
-        <v>32175</v>
+        <v>24680</v>
       </c>
       <c r="G35" s="0">
-        <v>0.82999999999999996</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="H35" s="0">
-        <v>4.8099999999999996</v>
+        <v>10.359999999999999</v>
       </c>
       <c r="I35" s="0">
-        <v>66</v>
+        <v>48.369999999999997</v>
       </c>
       <c r="J35" s="0">
-        <v>2714</v>
+        <v>4616</v>
       </c>
       <c r="K35" s="0">
-        <v>13830.23</v>
+        <v>10128.32</v>
       </c>
       <c r="L35" s="0">
-        <v>51.350000000000001</v>
+        <v>39.579999999999998</v>
       </c>
       <c r="M35" s="0">
-        <v>0.11</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="36">
@@ -1663,40 +1669,40 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>11801825315</v>
+        <v>4483167344</v>
       </c>
       <c r="C36" s="0">
-        <v>19558130434</v>
+        <v>7695296310</v>
       </c>
       <c r="D36" s="0">
-        <v>1273316</v>
+        <v>1626913</v>
       </c>
       <c r="E36" s="0">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F36" s="0">
-        <v>16704</v>
+        <v>6255</v>
       </c>
       <c r="G36" s="0">
-        <v>1.0900000000000001</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="H36" s="0">
-        <v>8.0999999999999996</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="I36" s="0">
-        <v>60.340000000000003</v>
+        <v>58.259999999999998</v>
       </c>
       <c r="J36" s="0">
-        <v>3652</v>
+        <v>3869</v>
       </c>
       <c r="K36" s="0">
-        <v>14148.139999999999</v>
+        <v>7915.1300000000001</v>
       </c>
       <c r="L36" s="0">
-        <v>44.170000000000002</v>
+        <v>24.890000000000001</v>
       </c>
       <c r="M36" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="37">
@@ -1704,39 +1710,121 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>685497794958</v>
+        <v>15501115262</v>
       </c>
       <c r="C37" s="0">
-        <v>929802884475</v>
+        <v>23485493926</v>
       </c>
       <c r="D37" s="0">
-        <v>426163</v>
+        <v>607174</v>
       </c>
       <c r="E37" s="0">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c r="F37" s="0">
-        <v>6655805</v>
+        <v>32175</v>
       </c>
       <c r="G37" s="0">
+        <v>0.82999999999999996</v>
+      </c>
+      <c r="H37" s="0">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="I37" s="0">
+        <v>66</v>
+      </c>
+      <c r="J37" s="0">
+        <v>2714</v>
+      </c>
+      <c r="K37" s="0">
+        <v>13830.23</v>
+      </c>
+      <c r="L37" s="0">
+        <v>51.350000000000001</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0">
+        <v>11801825315</v>
+      </c>
+      <c r="C38" s="0">
+        <v>19558130434</v>
+      </c>
+      <c r="D38" s="0">
+        <v>1273316</v>
+      </c>
+      <c r="E38" s="0">
+        <v>320</v>
+      </c>
+      <c r="F38" s="0">
+        <v>16704</v>
+      </c>
+      <c r="G38" s="0">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="H38" s="0">
+        <v>8.0999999999999996</v>
+      </c>
+      <c r="I38" s="0">
+        <v>60.340000000000003</v>
+      </c>
+      <c r="J38" s="0">
+        <v>3652</v>
+      </c>
+      <c r="K38" s="0">
+        <v>14148.139999999999</v>
+      </c>
+      <c r="L38" s="0">
+        <v>44.170000000000002</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0.089999999999999997</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0">
+        <v>686691136978</v>
+      </c>
+      <c r="C39" s="0">
+        <v>931568059354</v>
+      </c>
+      <c r="D39" s="0">
+        <v>422520</v>
+      </c>
+      <c r="E39" s="0">
+        <v>132</v>
+      </c>
+      <c r="F39" s="0">
+        <v>6721858</v>
+      </c>
+      <c r="G39" s="0">
         <v>3.0499999999999998</v>
       </c>
-      <c r="H37" s="0">
-        <v>7.3600000000000003</v>
-      </c>
-      <c r="I37" s="0">
-        <v>73.730000000000004</v>
-      </c>
-      <c r="J37" s="0">
-        <v>886</v>
-      </c>
-      <c r="K37" s="0">
-        <v>4378.2799999999997</v>
-      </c>
-      <c r="L37" s="0">
-        <v>29.27</v>
-      </c>
-      <c r="M37" s="0">
+      <c r="H39" s="0">
+        <v>7.3200000000000003</v>
+      </c>
+      <c r="I39" s="0">
+        <v>73.709999999999994</v>
+      </c>
+      <c r="J39" s="0">
+        <v>880</v>
+      </c>
+      <c r="K39" s="0">
+        <v>4365.1000000000004</v>
+      </c>
+      <c r="L39" s="0">
+        <v>29.260000000000002</v>
+      </c>
+      <c r="M39" s="0">
         <v>0.075999999999999998</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Aircraft_Cumulative_Statistics_2021.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Aircraft_Cumulative_Statistics_2021.xlsx
@@ -13,41 +13,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>E140</t>
-  </si>
-  <si>
-    <t>E145</t>
-  </si>
-  <si>
-    <t>CRJ-200</t>
-  </si>
-  <si>
-    <t>E170</t>
-  </si>
-  <si>
-    <t>E175</t>
-  </si>
-  <si>
-    <t>Q400</t>
-  </si>
-  <si>
-    <t>CRJ-550</t>
-  </si>
-  <si>
-    <t>CRJ-700</t>
-  </si>
-  <si>
-    <t>E190</t>
-  </si>
-  <si>
-    <t>CRJ-900</t>
-  </si>
-  <si>
     <t>A220-100</t>
   </si>
   <si>
@@ -58,9 +28,6 @@
   </si>
   <si>
     <t>A320</t>
-  </si>
-  <si>
-    <t>A320NEO</t>
   </si>
   <si>
     <t>A321</t>
@@ -211,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -234,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2">
@@ -275,40 +242,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>37931824</v>
+        <v>3319238941</v>
       </c>
       <c r="C2" s="0">
-        <v>62273728</v>
+        <v>4353176458</v>
       </c>
       <c r="D2" s="0">
-        <v>23589</v>
+        <v>296740</v>
       </c>
       <c r="E2" s="0">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F2" s="0">
-        <v>4960</v>
+        <v>40951</v>
       </c>
       <c r="G2" s="0">
-        <v>1.8799999999999999</v>
+        <v>2.79</v>
       </c>
       <c r="H2" s="0">
-        <v>2.4700000000000002</v>
+        <v>7.29</v>
       </c>
       <c r="I2" s="0">
-        <v>60.909999999999997</v>
+        <v>76.25</v>
       </c>
       <c r="J2" s="0">
-        <v>285</v>
+        <v>975</v>
       </c>
       <c r="K2" s="0">
-        <v>1551.46</v>
+        <v>4416.4200000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>35.259999999999998</v>
+        <v>40.530000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>0.16200000000000001</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="3">
@@ -316,40 +283,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>3562562849</v>
+        <v>818737091</v>
       </c>
       <c r="C3" s="0">
-        <v>4655109479</v>
+        <v>1125033859</v>
       </c>
       <c r="D3" s="0">
-        <v>48842</v>
+        <v>378799</v>
       </c>
       <c r="E3" s="0">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F3" s="0">
-        <v>280413</v>
+        <v>9255</v>
       </c>
       <c r="G3" s="0">
-        <v>2.9399999999999999</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="H3" s="0">
-        <v>4.2199999999999998</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="I3" s="0">
-        <v>76.530000000000001</v>
+        <v>72.769999999999996</v>
       </c>
       <c r="J3" s="0">
-        <v>332</v>
+        <v>935</v>
       </c>
       <c r="K3" s="0">
-        <v>1588.6700000000001</v>
+        <v>4444.8800000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>31.780000000000001</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M3" s="0">
-        <v>0.13700000000000001</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="4">
@@ -357,40 +324,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>3589076503</v>
+        <v>23255013613</v>
       </c>
       <c r="C4" s="0">
-        <v>5144234346</v>
+        <v>30191436173</v>
       </c>
       <c r="D4" s="0">
-        <v>56117</v>
+        <v>308296</v>
       </c>
       <c r="E4" s="0">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F4" s="0">
-        <v>288283</v>
+        <v>282236</v>
       </c>
       <c r="G4" s="0">
-        <v>3.1400000000000001</v>
+        <v>2.8799999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>4.3300000000000001</v>
+        <v>6.7300000000000004</v>
       </c>
       <c r="I4" s="0">
-        <v>69.769999999999996</v>
+        <v>77.030000000000001</v>
       </c>
       <c r="J4" s="0">
-        <v>357</v>
+        <v>834</v>
       </c>
       <c r="K4" s="0">
-        <v>2296.3499999999999</v>
+        <v>4547.5299999999997</v>
       </c>
       <c r="L4" s="0">
-        <v>45.93</v>
+        <v>35.460000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.17699999999999999</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="5">
@@ -398,40 +365,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>1598831898</v>
+        <v>20058834398</v>
       </c>
       <c r="C5" s="0">
-        <v>2014598782</v>
+        <v>26473519742</v>
       </c>
       <c r="D5" s="0">
-        <v>89737</v>
+        <v>366213</v>
       </c>
       <c r="E5" s="0">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="F5" s="0">
-        <v>48856</v>
+        <v>203500</v>
       </c>
       <c r="G5" s="0">
-        <v>2.1800000000000002</v>
+        <v>2.8199999999999998</v>
       </c>
       <c r="H5" s="0">
-        <v>4.3200000000000003</v>
+        <v>6.6200000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>79.359999999999999</v>
+        <v>75.769999999999996</v>
       </c>
       <c r="J5" s="0">
-        <v>591</v>
+        <v>854</v>
       </c>
       <c r="K5" s="0">
-        <v>1299.4100000000001</v>
+        <v>5161.7799999999997</v>
       </c>
       <c r="L5" s="0">
-        <v>18.620000000000001</v>
+        <v>33.899999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.063</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -439,40 +406,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>31383781010</v>
+        <v>60214998106</v>
       </c>
       <c r="C6" s="0">
-        <v>41540640374</v>
+        <v>75932918384</v>
       </c>
       <c r="D6" s="0">
-        <v>142800</v>
+        <v>624500</v>
       </c>
       <c r="E6" s="0">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="F6" s="0">
-        <v>906234</v>
+        <v>389497</v>
       </c>
       <c r="G6" s="0">
-        <v>3.1200000000000001</v>
+        <v>3.2000000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>6.0700000000000003</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="I6" s="0">
-        <v>75.549999999999997</v>
+        <v>79.299999999999997</v>
       </c>
       <c r="J6" s="0">
-        <v>614</v>
+        <v>1061</v>
       </c>
       <c r="K6" s="0">
-        <v>1379.3800000000001</v>
+        <v>5780.9700000000003</v>
       </c>
       <c r="L6" s="0">
-        <v>18.48</v>
+        <v>31.390000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.058999999999999997</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="7">
@@ -480,40 +447,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>930652685</v>
+        <v>8657819547</v>
       </c>
       <c r="C7" s="0">
-        <v>1335334896</v>
+        <v>11262067427</v>
       </c>
       <c r="D7" s="0">
-        <v>65618</v>
+        <v>887476</v>
       </c>
       <c r="E7" s="0">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="F7" s="0">
-        <v>57961</v>
+        <v>32151</v>
       </c>
       <c r="G7" s="0">
-        <v>2.8500000000000001</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H7" s="0">
-        <v>3.7000000000000002</v>
+        <v>10.539999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>69.689999999999998</v>
+        <v>76.879999999999995</v>
       </c>
       <c r="J7" s="0">
-        <v>303</v>
+        <v>1787</v>
       </c>
       <c r="K7" s="0">
-        <v>2046.51</v>
+        <v>6628.2700000000004</v>
       </c>
       <c r="L7" s="0">
-        <v>26.93</v>
+        <v>33.82</v>
       </c>
       <c r="M7" s="0">
-        <v>0.115</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -521,40 +488,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>1004554080</v>
+        <v>3321639943</v>
       </c>
       <c r="C8" s="0">
-        <v>1241697900</v>
+        <v>4449327759</v>
       </c>
       <c r="D8" s="0">
-        <v>69137</v>
+        <v>237297</v>
       </c>
       <c r="E8" s="0">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="F8" s="0">
-        <v>59901</v>
+        <v>88010</v>
       </c>
       <c r="G8" s="0">
-        <v>3.3399999999999999</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="H8" s="0">
-        <v>5.3499999999999996</v>
+        <v>7.0300000000000002</v>
       </c>
       <c r="I8" s="0">
-        <v>80.900000000000006</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="J8" s="0">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="K8" s="0">
-        <v>2045.0999999999999</v>
+        <v>4496.0500000000002</v>
       </c>
       <c r="L8" s="0">
-        <v>40.899999999999999</v>
+        <v>40.880000000000003</v>
       </c>
       <c r="M8" s="0">
-        <v>0.158</v>
+        <v>0.13300000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -562,37 +529,37 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>6714160960</v>
+        <v>3996682109</v>
       </c>
       <c r="C9" s="0">
-        <v>8944331084</v>
+        <v>5275509372</v>
       </c>
       <c r="D9" s="0">
-        <v>117813</v>
+        <v>329513</v>
       </c>
       <c r="E9" s="0">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F9" s="0">
-        <v>274585</v>
+        <v>36656</v>
       </c>
       <c r="G9" s="0">
-        <v>3.6200000000000001</v>
+        <v>2.29</v>
       </c>
       <c r="H9" s="0">
-        <v>6.2300000000000004</v>
+        <v>6.7999999999999998</v>
       </c>
       <c r="I9" s="0">
-        <v>75.069999999999993</v>
+        <v>75.760000000000005</v>
       </c>
       <c r="J9" s="0">
-        <v>495</v>
+        <v>1142</v>
       </c>
       <c r="K9" s="0">
-        <v>1944.04</v>
+        <v>5010.4799999999996</v>
       </c>
       <c r="L9" s="0">
-        <v>29.539999999999999</v>
+        <v>39.770000000000003</v>
       </c>
       <c r="M9" s="0">
         <v>0.10299999999999999</v>
@@ -603,40 +570,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>3549912290</v>
+        <v>68696380241</v>
       </c>
       <c r="C10" s="0">
-        <v>4709209138</v>
+        <v>90177359161</v>
       </c>
       <c r="D10" s="0">
-        <v>215032</v>
+        <v>520925</v>
       </c>
       <c r="E10" s="0">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="F10" s="0">
-        <v>73074</v>
+        <v>502183</v>
       </c>
       <c r="G10" s="0">
-        <v>3.3399999999999999</v>
+        <v>2.8999999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>6.5300000000000002</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="I10" s="0">
-        <v>75.379999999999995</v>
+        <v>76.180000000000007</v>
       </c>
       <c r="J10" s="0">
-        <v>642</v>
+        <v>1067</v>
       </c>
       <c r="K10" s="0">
-        <v>4575.6700000000001</v>
+        <v>5246.7600000000002</v>
       </c>
       <c r="L10" s="0">
-        <v>45.619999999999997</v>
+        <v>31.16</v>
       </c>
       <c r="M10" s="0">
-        <v>0.13900000000000001</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="11">
@@ -644,40 +611,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>12010167044</v>
+        <v>7010827744</v>
       </c>
       <c r="C11" s="0">
-        <v>15999576473</v>
+        <v>8763786670</v>
       </c>
       <c r="D11" s="0">
-        <v>161743</v>
+        <v>509819</v>
       </c>
       <c r="E11" s="0">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="F11" s="0">
-        <v>446531</v>
+        <v>44822</v>
       </c>
       <c r="G11" s="0">
-        <v>4.5099999999999998</v>
+        <v>2.6099999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>7.4100000000000001</v>
+        <v>7.7699999999999996</v>
       </c>
       <c r="I11" s="0">
-        <v>75.069999999999993</v>
+        <v>80</v>
       </c>
       <c r="J11" s="0">
-        <v>474</v>
+        <v>1142</v>
       </c>
       <c r="K11" s="0">
-        <v>1513.45</v>
+        <v>5215.0799999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>20.030000000000001</v>
+        <v>30.460000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -685,40 +652,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>3319238941</v>
+        <v>26291609</v>
       </c>
       <c r="C12" s="0">
-        <v>4353176458</v>
+        <v>30999399</v>
       </c>
       <c r="D12" s="0">
-        <v>296740</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="F12" s="0">
-        <v>40951</v>
+        <v>164</v>
       </c>
       <c r="G12" s="0">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="H12" s="0">
-        <v>7.29</v>
+        <v>0</v>
       </c>
       <c r="I12" s="0">
-        <v>76.25</v>
+        <v>84.810000000000002</v>
       </c>
       <c r="J12" s="0">
-        <v>975</v>
+        <v>1056</v>
       </c>
       <c r="K12" s="0">
-        <v>4416.4200000000001</v>
+        <v>0</v>
       </c>
       <c r="L12" s="0">
-        <v>40.530000000000001</v>
+        <v>0</v>
       </c>
       <c r="M12" s="0">
-        <v>0.108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -726,40 +693,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>1187889565</v>
+        <v>45338330471</v>
       </c>
       <c r="C13" s="0">
-        <v>1558931519</v>
+        <v>59609879773</v>
       </c>
       <c r="D13" s="0">
-        <v>385874</v>
+        <v>606902</v>
       </c>
       <c r="E13" s="0">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="F13" s="0">
-        <v>11756</v>
+        <v>288287</v>
       </c>
       <c r="G13" s="0">
-        <v>2.9100000000000001</v>
+        <v>2.9399999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>7.9000000000000004</v>
+        <v>8.5800000000000001</v>
       </c>
       <c r="I13" s="0">
-        <v>76.200000000000003</v>
+        <v>76.060000000000002</v>
       </c>
       <c r="J13" s="0">
-        <v>1000</v>
+        <v>1152</v>
       </c>
       <c r="K13" s="0">
-        <v>4434.75</v>
+        <v>4953.9300000000003</v>
       </c>
       <c r="L13" s="0">
-        <v>33.460000000000001</v>
+        <v>27.600000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="14">
@@ -767,40 +734,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>29748111048</v>
+        <v>5294217571</v>
       </c>
       <c r="C14" s="0">
-        <v>38967063060</v>
+        <v>6391513441</v>
       </c>
       <c r="D14" s="0">
-        <v>329922</v>
+        <v>588537</v>
       </c>
       <c r="E14" s="0">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="F14" s="0">
-        <v>344929</v>
+        <v>27417</v>
       </c>
       <c r="G14" s="0">
-        <v>2.9199999999999999</v>
+        <v>2.52</v>
       </c>
       <c r="H14" s="0">
-        <v>6.8799999999999999</v>
+        <v>8.1799999999999997</v>
       </c>
       <c r="I14" s="0">
-        <v>76.340000000000003</v>
+        <v>82.829999999999998</v>
       </c>
       <c r="J14" s="0">
-        <v>851</v>
+        <v>1302</v>
       </c>
       <c r="K14" s="0">
-        <v>4431.6000000000004</v>
+        <v>4312.9499999999998</v>
       </c>
       <c r="L14" s="0">
-        <v>33.450000000000003</v>
+        <v>24.09</v>
       </c>
       <c r="M14" s="0">
-        <v>0.091999999999999998</v>
+        <v>0.059999999999999998</v>
       </c>
     </row>
     <row r="15">
@@ -808,40 +775,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>66054316806</v>
+        <v>18861731702</v>
       </c>
       <c r="C15" s="0">
-        <v>87801329700</v>
+        <v>26093310801</v>
       </c>
       <c r="D15" s="0">
-        <v>478195</v>
+        <v>515882</v>
       </c>
       <c r="E15" s="0">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="F15" s="0">
-        <v>540471</v>
+        <v>100671</v>
       </c>
       <c r="G15" s="0">
-        <v>2.9399999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="H15" s="0">
-        <v>7.7000000000000002</v>
+        <v>6.7599999999999998</v>
       </c>
       <c r="I15" s="0">
-        <v>75.230000000000004</v>
+        <v>72.290000000000006</v>
       </c>
       <c r="J15" s="0">
-        <v>988</v>
+        <v>1399</v>
       </c>
       <c r="K15" s="0">
-        <v>4896.0200000000004</v>
+        <v>5730.1000000000004</v>
       </c>
       <c r="L15" s="0">
-        <v>29.800000000000001</v>
+        <v>30.93</v>
       </c>
       <c r="M15" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="16">
@@ -849,40 +816,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>21123211863</v>
+        <v>8141345162</v>
       </c>
       <c r="C16" s="0">
-        <v>27477820744</v>
+        <v>10413787531</v>
       </c>
       <c r="D16" s="0">
-        <v>670845</v>
+        <v>775990</v>
       </c>
       <c r="E16" s="0">
-        <v>185</v>
+        <v>234</v>
       </c>
       <c r="F16" s="0">
-        <v>147702</v>
+        <v>31591</v>
       </c>
       <c r="G16" s="0">
-        <v>3.6099999999999999</v>
+        <v>2.3500000000000001</v>
       </c>
       <c r="H16" s="0">
-        <v>9.7899999999999991</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="I16" s="0">
-        <v>76.870000000000005</v>
+        <v>78.180000000000007</v>
       </c>
       <c r="J16" s="0">
-        <v>1009</v>
+        <v>1409</v>
       </c>
       <c r="K16" s="0">
-        <v>4174.4300000000003</v>
+        <v>6154.2600000000002</v>
       </c>
       <c r="L16" s="0">
-        <v>22.629999999999999</v>
+        <v>26.300000000000001</v>
       </c>
       <c r="M16" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -890,40 +857,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>87086883349</v>
+        <v>12826273084</v>
       </c>
       <c r="C17" s="0">
-        <v>110394550101</v>
+        <v>17349402679</v>
       </c>
       <c r="D17" s="0">
-        <v>669301</v>
+        <v>630200</v>
       </c>
       <c r="E17" s="0">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="F17" s="0">
-        <v>512547</v>
+        <v>35343</v>
       </c>
       <c r="G17" s="0">
-        <v>3.1099999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="H17" s="0">
-        <v>9.1699999999999999</v>
+        <v>6.7599999999999998</v>
       </c>
       <c r="I17" s="0">
-        <v>78.890000000000001</v>
+        <v>73.930000000000007</v>
       </c>
       <c r="J17" s="0">
-        <v>1148</v>
+        <v>2379</v>
       </c>
       <c r="K17" s="0">
-        <v>5336.0200000000004</v>
+        <v>7566.1099999999997</v>
       </c>
       <c r="L17" s="0">
-        <v>28.309999999999999</v>
+        <v>36.600000000000001</v>
       </c>
       <c r="M17" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="18">
@@ -931,40 +898,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>18350821703</v>
+        <v>7118188954</v>
       </c>
       <c r="C18" s="0">
-        <v>24523726632</v>
+        <v>9596172675</v>
       </c>
       <c r="D18" s="0">
-        <v>879617</v>
+        <v>803027</v>
       </c>
       <c r="E18" s="0">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="F18" s="0">
-        <v>68317</v>
+        <v>17007</v>
       </c>
       <c r="G18" s="0">
-        <v>2.4500000000000002</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>10.59</v>
+        <v>7.4800000000000004</v>
       </c>
       <c r="I18" s="0">
-        <v>74.829999999999998</v>
+        <v>74.180000000000007</v>
       </c>
       <c r="J18" s="0">
-        <v>1857</v>
+        <v>2390</v>
       </c>
       <c r="K18" s="0">
-        <v>5318.9099999999999</v>
+        <v>6796.04</v>
       </c>
       <c r="L18" s="0">
-        <v>27.489999999999998</v>
+        <v>28.780000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="19">
@@ -972,40 +939,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>3741015240</v>
+        <v>2299323070</v>
       </c>
       <c r="C19" s="0">
-        <v>5152156687</v>
+        <v>3036658066</v>
       </c>
       <c r="D19" s="0">
-        <v>200239</v>
+        <v>764901</v>
       </c>
       <c r="E19" s="0">
-        <v>116</v>
+        <v>231</v>
       </c>
       <c r="F19" s="0">
-        <v>127759</v>
+        <v>5024</v>
       </c>
       <c r="G19" s="0">
-        <v>4.9699999999999998</v>
+        <v>1.27</v>
       </c>
       <c r="H19" s="0">
-        <v>6.2400000000000002</v>
+        <v>7.1699999999999999</v>
       </c>
       <c r="I19" s="0">
-        <v>72.609999999999999</v>
+        <v>75.719999999999999</v>
       </c>
       <c r="J19" s="0">
-        <v>360</v>
+        <v>2613</v>
       </c>
       <c r="K19" s="0">
-        <v>4668.29</v>
+        <v>7681.3999999999996</v>
       </c>
       <c r="L19" s="0">
-        <v>41.229999999999997</v>
+        <v>33.210000000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0.14499999999999999</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="20">
@@ -1013,40 +980,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>60131029150</v>
+        <v>9183762268</v>
       </c>
       <c r="C20" s="0">
-        <v>76187565600</v>
+        <v>15211539946</v>
       </c>
       <c r="D20" s="0">
-        <v>403814</v>
+        <v>1363041</v>
       </c>
       <c r="E20" s="0">
-        <v>142</v>
+        <v>291</v>
       </c>
       <c r="F20" s="0">
-        <v>716071</v>
+        <v>15724</v>
       </c>
       <c r="G20" s="0">
-        <v>3.7999999999999998</v>
+        <v>1.4099999999999999</v>
       </c>
       <c r="H20" s="0">
-        <v>7.7699999999999996</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="I20" s="0">
-        <v>78.920000000000002</v>
+        <v>60.369999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>753</v>
+        <v>3326</v>
       </c>
       <c r="K20" s="0">
-        <v>4231.2600000000002</v>
+        <v>7911.8699999999999</v>
       </c>
       <c r="L20" s="0">
-        <v>29.920000000000002</v>
+        <v>27.199999999999999</v>
       </c>
       <c r="M20" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="21">
@@ -1054,40 +1021,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>121649794708</v>
+        <v>2901906828</v>
       </c>
       <c r="C21" s="0">
-        <v>159663333974</v>
+        <v>5703460033</v>
       </c>
       <c r="D21" s="0">
-        <v>560458</v>
+        <v>1584294</v>
       </c>
       <c r="E21" s="0">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="F21" s="0">
-        <v>918296</v>
+        <v>4652</v>
       </c>
       <c r="G21" s="0">
-        <v>3.2200000000000002</v>
+        <v>1.29</v>
       </c>
       <c r="H21" s="0">
-        <v>8.5500000000000007</v>
+        <v>11.539999999999999</v>
       </c>
       <c r="I21" s="0">
-        <v>76.189999999999998</v>
+        <v>50.880000000000003</v>
       </c>
       <c r="J21" s="0">
-        <v>1023</v>
+        <v>4385</v>
       </c>
       <c r="K21" s="0">
-        <v>4689.5900000000001</v>
+        <v>7883.3800000000001</v>
       </c>
       <c r="L21" s="0">
-        <v>27.559999999999999</v>
+        <v>28.190000000000001</v>
       </c>
       <c r="M21" s="0">
-        <v>0.071999999999999995</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="22">
@@ -1095,40 +1062,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>16184520330</v>
+        <v>3381554723</v>
       </c>
       <c r="C22" s="0">
-        <v>20867478445</v>
+        <v>9377588714</v>
       </c>
       <c r="D22" s="0">
-        <v>524968</v>
+        <v>1502819</v>
       </c>
       <c r="E22" s="0">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="F22" s="0">
-        <v>113589</v>
+        <v>5796</v>
       </c>
       <c r="G22" s="0">
-        <v>2.8599999999999999</v>
+        <v>0.93000000000000005</v>
       </c>
       <c r="H22" s="0">
-        <v>7.75</v>
+        <v>9.6899999999999995</v>
       </c>
       <c r="I22" s="0">
-        <v>77.560000000000002</v>
+        <v>36.060000000000002</v>
       </c>
       <c r="J22" s="0">
-        <v>1060</v>
+        <v>5341</v>
       </c>
       <c r="K22" s="0">
-        <v>4442.3800000000001</v>
+        <v>8668.5300000000007</v>
       </c>
       <c r="L22" s="0">
-        <v>25.629999999999999</v>
+        <v>28.609999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1136,40 +1103,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>1440587229</v>
+        <v>7835936452</v>
       </c>
       <c r="C23" s="0">
-        <v>1880841971</v>
+        <v>12581643851</v>
       </c>
       <c r="D23" s="0">
-        <v>563126</v>
+        <v>970057</v>
       </c>
       <c r="E23" s="0">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="F23" s="0">
-        <v>10559</v>
+        <v>18502</v>
       </c>
       <c r="G23" s="0">
-        <v>3.1600000000000001</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H23" s="0">
-        <v>8.5600000000000005</v>
+        <v>8.8499999999999996</v>
       </c>
       <c r="I23" s="0">
-        <v>76.590000000000003</v>
+        <v>62.280000000000001</v>
       </c>
       <c r="J23" s="0">
-        <v>1001</v>
+        <v>2996</v>
       </c>
       <c r="K23" s="0">
-        <v>4423.96</v>
+        <v>9788.7099999999991</v>
       </c>
       <c r="L23" s="0">
-        <v>24.859999999999999</v>
+        <v>43.090000000000003</v>
       </c>
       <c r="M23" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="24">
@@ -1177,40 +1144,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>61646356697</v>
+        <v>14099923633</v>
       </c>
       <c r="C24" s="0">
-        <v>81628279523</v>
+        <v>29148468899</v>
       </c>
       <c r="D24" s="0">
-        <v>642793</v>
+        <v>1342629</v>
       </c>
       <c r="E24" s="0">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F24" s="0">
-        <v>371593</v>
+        <v>24680</v>
       </c>
       <c r="G24" s="0">
-        <v>2.9300000000000002</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="H24" s="0">
-        <v>9.0299999999999994</v>
+        <v>10.359999999999999</v>
       </c>
       <c r="I24" s="0">
-        <v>75.519999999999996</v>
+        <v>48.369999999999997</v>
       </c>
       <c r="J24" s="0">
-        <v>1227</v>
+        <v>4616</v>
       </c>
       <c r="K24" s="0">
-        <v>4562.8000000000002</v>
+        <v>10128.32</v>
       </c>
       <c r="L24" s="0">
-        <v>25.48</v>
+        <v>39.579999999999998</v>
       </c>
       <c r="M24" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="25">
@@ -1218,40 +1185,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>6110662648</v>
+        <v>4483167344</v>
       </c>
       <c r="C25" s="0">
-        <v>7446208119</v>
+        <v>7695296310</v>
       </c>
       <c r="D25" s="0">
-        <v>596174</v>
+        <v>1626913</v>
       </c>
       <c r="E25" s="0">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="F25" s="0">
-        <v>31603</v>
+        <v>6255</v>
       </c>
       <c r="G25" s="0">
-        <v>2.5299999999999998</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="H25" s="0">
-        <v>8.3100000000000005</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="I25" s="0">
-        <v>82.060000000000002</v>
+        <v>58.259999999999998</v>
       </c>
       <c r="J25" s="0">
-        <v>1317</v>
+        <v>3869</v>
       </c>
       <c r="K25" s="0">
-        <v>4038.4299999999998</v>
+        <v>7915.1300000000001</v>
       </c>
       <c r="L25" s="0">
-        <v>22.579999999999998</v>
+        <v>24.890000000000001</v>
       </c>
       <c r="M25" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="26">
@@ -1259,40 +1226,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>18861731702</v>
+        <v>15501115262</v>
       </c>
       <c r="C26" s="0">
-        <v>26093310801</v>
+        <v>23485493926</v>
       </c>
       <c r="D26" s="0">
-        <v>515882</v>
+        <v>607174</v>
       </c>
       <c r="E26" s="0">
-        <v>186</v>
+        <v>272</v>
       </c>
       <c r="F26" s="0">
-        <v>100671</v>
+        <v>32175</v>
       </c>
       <c r="G26" s="0">
-        <v>1.99</v>
+        <v>0.82999999999999996</v>
       </c>
       <c r="H26" s="0">
-        <v>6.7599999999999998</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="I26" s="0">
-        <v>72.290000000000006</v>
+        <v>66</v>
       </c>
       <c r="J26" s="0">
-        <v>1399</v>
+        <v>2714</v>
       </c>
       <c r="K26" s="0">
-        <v>5730.1000000000004</v>
+        <v>13830.23</v>
       </c>
       <c r="L26" s="0">
-        <v>30.93</v>
+        <v>51.350000000000001</v>
       </c>
       <c r="M26" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="27">
@@ -1300,40 +1267,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>8141345162</v>
+        <v>11801825315</v>
       </c>
       <c r="C27" s="0">
-        <v>10413787531</v>
+        <v>19558130434</v>
       </c>
       <c r="D27" s="0">
-        <v>775990</v>
+        <v>1273316</v>
       </c>
       <c r="E27" s="0">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="F27" s="0">
-        <v>31591</v>
+        <v>16704</v>
       </c>
       <c r="G27" s="0">
-        <v>2.3500000000000001</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="H27" s="0">
-        <v>8.0399999999999991</v>
+        <v>8.0999999999999996</v>
       </c>
       <c r="I27" s="0">
-        <v>78.180000000000007</v>
+        <v>60.340000000000003</v>
       </c>
       <c r="J27" s="0">
-        <v>1409</v>
+        <v>3652</v>
       </c>
       <c r="K27" s="0">
-        <v>6154.2600000000002</v>
+        <v>14148.139999999999</v>
       </c>
       <c r="L27" s="0">
-        <v>26.300000000000001</v>
+        <v>44.170000000000002</v>
       </c>
       <c r="M27" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="28">
@@ -1341,491 +1308,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>12826273084</v>
+        <v>368445065181</v>
       </c>
       <c r="C28" s="0">
-        <v>17349402679</v>
+        <v>513287481483</v>
       </c>
       <c r="D28" s="0">
-        <v>630200</v>
+        <v>584490</v>
       </c>
       <c r="E28" s="0">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="F28" s="0">
-        <v>35343</v>
+        <v>2259253</v>
       </c>
       <c r="G28" s="0">
-        <v>1.28</v>
+        <v>2.5699999999999998</v>
       </c>
       <c r="H28" s="0">
-        <v>6.7599999999999998</v>
+        <v>7.8099999999999996</v>
       </c>
       <c r="I28" s="0">
-        <v>73.930000000000007</v>
+        <v>71.780000000000001</v>
       </c>
       <c r="J28" s="0">
-        <v>2379</v>
+        <v>1210</v>
       </c>
       <c r="K28" s="0">
-        <v>7581.1999999999998</v>
+        <v>6071.3400000000001</v>
       </c>
       <c r="L28" s="0">
-        <v>36.68</v>
+        <v>33.100000000000001</v>
       </c>
       <c r="M28" s="0">
         <v>0.081000000000000003</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="0">
-        <v>7118188954</v>
-      </c>
-      <c r="C29" s="0">
-        <v>9596172675</v>
-      </c>
-      <c r="D29" s="0">
-        <v>803027</v>
-      </c>
-      <c r="E29" s="0">
-        <v>236</v>
-      </c>
-      <c r="F29" s="0">
-        <v>17007</v>
-      </c>
-      <c r="G29" s="0">
-        <v>1.4199999999999999</v>
-      </c>
-      <c r="H29" s="0">
-        <v>7.4800000000000004</v>
-      </c>
-      <c r="I29" s="0">
-        <v>74.180000000000007</v>
-      </c>
-      <c r="J29" s="0">
-        <v>2390</v>
-      </c>
-      <c r="K29" s="0">
-        <v>6796.04</v>
-      </c>
-      <c r="L29" s="0">
-        <v>28.780000000000001</v>
-      </c>
-      <c r="M29" s="0">
-        <v>0.063</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="0">
-        <v>8398335831</v>
-      </c>
-      <c r="C30" s="0">
-        <v>11804294822</v>
-      </c>
-      <c r="D30" s="0">
-        <v>923654</v>
-      </c>
-      <c r="E30" s="0">
-        <v>258</v>
-      </c>
-      <c r="F30" s="0">
-        <v>15817</v>
-      </c>
-      <c r="G30" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H30" s="0">
-        <v>7.6399999999999997</v>
-      </c>
-      <c r="I30" s="0">
-        <v>71.150000000000006</v>
-      </c>
-      <c r="J30" s="0">
-        <v>2874</v>
-      </c>
-      <c r="K30" s="0">
-        <v>8857.8799999999992</v>
-      </c>
-      <c r="L30" s="0">
-        <v>34.140000000000001</v>
-      </c>
-      <c r="M30" s="0">
-        <v>0.072999999999999995</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="0">
-        <v>9183762268</v>
-      </c>
-      <c r="C31" s="0">
-        <v>15211539946</v>
-      </c>
-      <c r="D31" s="0">
-        <v>1363041</v>
-      </c>
-      <c r="E31" s="0">
-        <v>291</v>
-      </c>
-      <c r="F31" s="0">
-        <v>15724</v>
-      </c>
-      <c r="G31" s="0">
-        <v>1.4099999999999999</v>
-      </c>
-      <c r="H31" s="0">
-        <v>9.8699999999999992</v>
-      </c>
-      <c r="I31" s="0">
-        <v>60.369999999999997</v>
-      </c>
-      <c r="J31" s="0">
-        <v>3326</v>
-      </c>
-      <c r="K31" s="0">
-        <v>7911.8699999999999</v>
-      </c>
-      <c r="L31" s="0">
-        <v>27.199999999999999</v>
-      </c>
-      <c r="M31" s="0">
-        <v>0.057000000000000002</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="0">
-        <v>2901906828</v>
-      </c>
-      <c r="C32" s="0">
-        <v>5703460033</v>
-      </c>
-      <c r="D32" s="0">
-        <v>1584294</v>
-      </c>
-      <c r="E32" s="0">
-        <v>280</v>
-      </c>
-      <c r="F32" s="0">
-        <v>4652</v>
-      </c>
-      <c r="G32" s="0">
-        <v>1.29</v>
-      </c>
-      <c r="H32" s="0">
-        <v>11.539999999999999</v>
-      </c>
-      <c r="I32" s="0">
-        <v>50.880000000000003</v>
-      </c>
-      <c r="J32" s="0">
-        <v>4385</v>
-      </c>
-      <c r="K32" s="0">
-        <v>7883.3800000000001</v>
-      </c>
-      <c r="L32" s="0">
-        <v>28.190000000000001</v>
-      </c>
-      <c r="M32" s="0">
-        <v>0.057000000000000002</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="0">
-        <v>3381554723</v>
-      </c>
-      <c r="C33" s="0">
-        <v>9377588714</v>
-      </c>
-      <c r="D33" s="0">
-        <v>1502819</v>
-      </c>
-      <c r="E33" s="0">
-        <v>303</v>
-      </c>
-      <c r="F33" s="0">
-        <v>5796</v>
-      </c>
-      <c r="G33" s="0">
-        <v>0.93000000000000005</v>
-      </c>
-      <c r="H33" s="0">
-        <v>9.6899999999999995</v>
-      </c>
-      <c r="I33" s="0">
-        <v>36.060000000000002</v>
-      </c>
-      <c r="J33" s="0">
-        <v>5341</v>
-      </c>
-      <c r="K33" s="0">
-        <v>8668.5300000000007</v>
-      </c>
-      <c r="L33" s="0">
-        <v>28.609999999999999</v>
-      </c>
-      <c r="M33" s="0">
-        <v>0.056000000000000001</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="0">
-        <v>7835936452</v>
-      </c>
-      <c r="C34" s="0">
-        <v>12581643851</v>
-      </c>
-      <c r="D34" s="0">
-        <v>970057</v>
-      </c>
-      <c r="E34" s="0">
-        <v>232</v>
-      </c>
-      <c r="F34" s="0">
-        <v>18502</v>
-      </c>
-      <c r="G34" s="0">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="H34" s="0">
-        <v>8.8499999999999996</v>
-      </c>
-      <c r="I34" s="0">
-        <v>62.280000000000001</v>
-      </c>
-      <c r="J34" s="0">
-        <v>2996</v>
-      </c>
-      <c r="K34" s="0">
-        <v>9788.7099999999991</v>
-      </c>
-      <c r="L34" s="0">
-        <v>43.090000000000003</v>
-      </c>
-      <c r="M34" s="0">
-        <v>0.088999999999999996</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="0">
-        <v>14099923633</v>
-      </c>
-      <c r="C35" s="0">
-        <v>29148468899</v>
-      </c>
-      <c r="D35" s="0">
-        <v>1342629</v>
-      </c>
-      <c r="E35" s="0">
-        <v>260</v>
-      </c>
-      <c r="F35" s="0">
-        <v>24680</v>
-      </c>
-      <c r="G35" s="0">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="H35" s="0">
-        <v>10.359999999999999</v>
-      </c>
-      <c r="I35" s="0">
-        <v>48.369999999999997</v>
-      </c>
-      <c r="J35" s="0">
-        <v>4616</v>
-      </c>
-      <c r="K35" s="0">
-        <v>10128.32</v>
-      </c>
-      <c r="L35" s="0">
-        <v>39.579999999999998</v>
-      </c>
-      <c r="M35" s="0">
-        <v>0.078</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="0">
-        <v>4483167344</v>
-      </c>
-      <c r="C36" s="0">
-        <v>7695296310</v>
-      </c>
-      <c r="D36" s="0">
-        <v>1626913</v>
-      </c>
-      <c r="E36" s="0">
-        <v>318</v>
-      </c>
-      <c r="F36" s="0">
-        <v>6255</v>
-      </c>
-      <c r="G36" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="H36" s="0">
-        <v>10.210000000000001</v>
-      </c>
-      <c r="I36" s="0">
-        <v>58.259999999999998</v>
-      </c>
-      <c r="J36" s="0">
-        <v>3869</v>
-      </c>
-      <c r="K36" s="0">
-        <v>7915.1300000000001</v>
-      </c>
-      <c r="L36" s="0">
-        <v>24.890000000000001</v>
-      </c>
-      <c r="M36" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="0">
-        <v>15501115262</v>
-      </c>
-      <c r="C37" s="0">
-        <v>23485493926</v>
-      </c>
-      <c r="D37" s="0">
-        <v>607174</v>
-      </c>
-      <c r="E37" s="0">
-        <v>272</v>
-      </c>
-      <c r="F37" s="0">
-        <v>32175</v>
-      </c>
-      <c r="G37" s="0">
-        <v>0.82999999999999996</v>
-      </c>
-      <c r="H37" s="0">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="I37" s="0">
-        <v>66</v>
-      </c>
-      <c r="J37" s="0">
-        <v>2714</v>
-      </c>
-      <c r="K37" s="0">
-        <v>13830.23</v>
-      </c>
-      <c r="L37" s="0">
-        <v>51.350000000000001</v>
-      </c>
-      <c r="M37" s="0">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="0">
-        <v>11801825315</v>
-      </c>
-      <c r="C38" s="0">
-        <v>19558130434</v>
-      </c>
-      <c r="D38" s="0">
-        <v>1273316</v>
-      </c>
-      <c r="E38" s="0">
-        <v>320</v>
-      </c>
-      <c r="F38" s="0">
-        <v>16704</v>
-      </c>
-      <c r="G38" s="0">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="H38" s="0">
-        <v>8.0999999999999996</v>
-      </c>
-      <c r="I38" s="0">
-        <v>60.340000000000003</v>
-      </c>
-      <c r="J38" s="0">
-        <v>3652</v>
-      </c>
-      <c r="K38" s="0">
-        <v>14148.139999999999</v>
-      </c>
-      <c r="L38" s="0">
-        <v>44.170000000000002</v>
-      </c>
-      <c r="M38" s="0">
-        <v>0.089999999999999997</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="0">
-        <v>686691136978</v>
-      </c>
-      <c r="C39" s="0">
-        <v>931568059354</v>
-      </c>
-      <c r="D39" s="0">
-        <v>422520</v>
-      </c>
-      <c r="E39" s="0">
-        <v>132</v>
-      </c>
-      <c r="F39" s="0">
-        <v>6721858</v>
-      </c>
-      <c r="G39" s="0">
-        <v>3.0499999999999998</v>
-      </c>
-      <c r="H39" s="0">
-        <v>7.3200000000000003</v>
-      </c>
-      <c r="I39" s="0">
-        <v>73.709999999999994</v>
-      </c>
-      <c r="J39" s="0">
-        <v>880</v>
-      </c>
-      <c r="K39" s="0">
-        <v>4365.1000000000004</v>
-      </c>
-      <c r="L39" s="0">
-        <v>29.260000000000002</v>
-      </c>
-      <c r="M39" s="0">
-        <v>0.075999999999999998</v>
       </c>
     </row>
   </sheetData>
